--- a/Запрещённые_предметы_по_неделям.xlsx
+++ b/Запрещённые_предметы_по_неделям.xlsx
@@ -26,7 +26,7 @@
     <author>&lt;анонимный&gt;</author>
   </authors>
   <commentList>
-    <comment ref="B73" authorId="0">
+    <comment ref="B80" authorId="0">
       <text>
         <r>
           <rPr>
@@ -191,7 +191,7 @@
     <numFmt numFmtId="170" formatCode="0.0000%"/>
     <numFmt numFmtId="171" formatCode="\+0.0000;\-0.0000;0.0000"/>
     <numFmt numFmtId="172" formatCode="dd/mm/yyyy"/>
-    <numFmt numFmtId="173" formatCode="[&lt;0.00005]0.000%;[&lt;0.0005]0.00%;0.0%"/>
+    <numFmt numFmtId="173" formatCode="[&lt;0.00005]0.0000%;[&lt;0.0005]0.00%;0.0%"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -796,8 +796,8 @@
         </c:ser>
         <c:gapWidth val="40"/>
         <c:overlap val="0"/>
-        <c:axId val="85365568"/>
-        <c:axId val="7659989"/>
+        <c:axId val="67739032"/>
+        <c:axId val="43901362"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -820,7 +820,7 @@
             <a:solidFill>
               <a:srgbClr val="C00000"/>
             </a:solidFill>
-            <a:ln w="22320">
+            <a:ln w="28440">
               <a:solidFill>
                 <a:srgbClr val="C00000"/>
               </a:solidFill>
@@ -858,7 +858,7 @@
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
-                <a:ln w="22320">
+                <a:ln w="28440">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -966,7 +966,7 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -986,7 +986,7 @@
             <a:solidFill>
               <a:srgbClr val="1F4E78"/>
             </a:solidFill>
-            <a:ln w="22320">
+            <a:ln w="28440">
               <a:solidFill>
                 <a:srgbClr val="1F4E78"/>
               </a:solidFill>
@@ -1024,7 +1024,7 @@
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
-                <a:ln w="22320">
+                <a:ln w="28440">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -1132,7 +1132,7 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
@@ -1152,7 +1152,7 @@
             <a:solidFill>
               <a:srgbClr val="70AD47"/>
             </a:solidFill>
-            <a:ln w="22320">
+            <a:ln w="28440">
               <a:solidFill>
                 <a:srgbClr val="70AD47"/>
               </a:solidFill>
@@ -1190,7 +1190,7 @@
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
-                <a:ln w="22320">
+                <a:ln w="28440">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -1298,7 +1298,7 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
         </c:ser>
         <c:ser>
           <c:idx val="4"/>
@@ -1318,7 +1318,7 @@
             <a:solidFill>
               <a:srgbClr val="ED7D31"/>
             </a:solidFill>
-            <a:ln w="22320">
+            <a:ln w="28440">
               <a:solidFill>
                 <a:srgbClr val="ED7D31"/>
               </a:solidFill>
@@ -1356,7 +1356,7 @@
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
-                <a:ln w="22320">
+                <a:ln w="28440">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -1464,7 +1464,7 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
         </c:ser>
         <c:ser>
           <c:idx val="5"/>
@@ -1484,7 +1484,7 @@
             <a:solidFill>
               <a:srgbClr val="7030A0"/>
             </a:solidFill>
-            <a:ln w="22320">
+            <a:ln w="28440">
               <a:solidFill>
                 <a:srgbClr val="7030A0"/>
               </a:solidFill>
@@ -1522,7 +1522,7 @@
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
-                <a:ln w="22320">
+                <a:ln w="28440">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -1630,7 +1630,7 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
         </c:ser>
         <c:ser>
           <c:idx val="6"/>
@@ -1650,7 +1650,7 @@
             <a:solidFill>
               <a:srgbClr val="000000"/>
             </a:solidFill>
-            <a:ln w="34920">
+            <a:ln w="38160">
               <a:solidFill>
                 <a:srgbClr val="000000"/>
               </a:solidFill>
@@ -1688,7 +1688,7 @@
             <c:showLeaderLines val="1"/>
             <c:leaderLines>
               <c:spPr>
-                <a:ln w="34920">
+                <a:ln w="38160">
                   <a:solidFill>
                     <a:srgbClr val="000000"/>
                   </a:solidFill>
@@ -1796,7 +1796,7 @@
               </c:numCache>
             </c:numRef>
           </c:val>
-          <c:smooth val="0"/>
+          <c:smooth val="1"/>
         </c:ser>
         <c:hiLowLines>
           <c:spPr>
@@ -1806,11 +1806,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="1618895"/>
-        <c:axId val="26507869"/>
+        <c:axId val="22705942"/>
+        <c:axId val="43986593"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="85365568"/>
+        <c:axId val="67739032"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1843,7 +1843,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7659989"/>
+        <c:crossAx val="43901362"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1851,7 +1851,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="7659989"/>
+        <c:axId val="43901362"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -1918,12 +1918,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85365568"/>
+        <c:crossAx val="67739032"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="1618895"/>
+        <c:axId val="22705942"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1956,7 +1956,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26507869"/>
+        <c:crossAx val="43986593"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1964,12 +1964,12 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="26507869"/>
+        <c:axId val="43986593"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
           <c:max val="0.01"/>
-          <c:min val="1E-005"/>
+          <c:min val="1E-006"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="r"/>
@@ -2006,7 +2006,7 @@
             </a:ln>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="[&lt;0.00005]0.000%;[&lt;0.0005]0.00%;0.0%" sourceLinked="0"/>
+        <c:numFmt formatCode="[&lt;0.00005]0.0000%;[&lt;0.0005]0.00%;0.0%" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -2033,7 +2033,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1618895"/>
+        <c:crossAx val="22705942"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2316,8 +2316,8 @@
     <xdr:to>
       <xdr:col>10</xdr:col>
       <xdr:colOff>861120</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>44640</xdr:rowOff>
+      <xdr:row>73</xdr:row>
+      <xdr:rowOff>151200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2326,7 +2326,7 @@
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
         <a:off x="0" y="7810560"/>
-        <a:ext cx="10799640" cy="5759640"/>
+        <a:ext cx="10799640" cy="7199640"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2519,7 +2519,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:P100"/>
+  <dimension ref="A1:P107"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
@@ -2536,12 +2536,12 @@
         <v>1</v>
       </c>
       <c r="B2" s="2" t="str">
-        <f aca="false">IF(Служебный!$K$2&lt;2,"-","Неделя "&amp;(Служебный!$K$2-1)&amp;": "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$B$73:$B$98,Служебный!$K$2-1)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$B$73:$B$98,Служебный!$K$2-1)),"00")&amp;" - "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$C$73:$C$98,Служебный!$K$2-1)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$C$73:$C$98,Служебный!$K$2-1)),"00"))</f>
+        <f aca="false">IF(Служебный!$K$2&lt;2,"-","Неделя "&amp;(Служебный!$K$2-1)&amp;": "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$B$80:$B$105,Служебный!$K$2-1)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$B$80:$B$105,Служебный!$K$2-1)),"00")&amp;" - "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$C$80:$C$105,Служебный!$K$2-1)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$C$80:$C$105,Служебный!$K$2-1)),"00"))</f>
         <v>-</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="str">
-        <f aca="false">IF(Служебный!$K$2&lt;1,"-","Неделя "&amp;(Служебный!$K$2-0)&amp;": "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$B$73:$B$98,Служебный!$K$2-0)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$B$73:$B$98,Служебный!$K$2-0)),"00")&amp;" - "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$C$73:$C$98,Служебный!$K$2-0)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$C$73:$C$98,Служебный!$K$2-0)),"00"))</f>
+        <f aca="false">IF(Служебный!$K$2&lt;1,"-","Неделя "&amp;(Служебный!$K$2-0)&amp;": "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$B$80:$B$105,Служебный!$K$2-0)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$B$80:$B$105,Служебный!$K$2-0)),"00")&amp;" - "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$C$80:$C$105,Служебный!$K$2-0)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$C$80:$C$105,Служебный!$K$2-0)),"00"))</f>
         <v>-</v>
       </c>
       <c r="E2" s="2"/>
@@ -2580,14 +2580,14 @@
         <v>8</v>
       </c>
       <c r="B4" s="4" t="str">
-        <f aca="false">IF(Служебный!$K$2&lt;2,"",INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$2-1))</f>
+        <f aca="false">IF(Служебный!$K$2&lt;2,"",INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$2-1))</f>
         <v/>
       </c>
       <c r="C4" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="4" t="str">
-        <f aca="false">IF(Служебный!$K$2&lt;1,"",INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$2))</f>
+        <f aca="false">IF(Служебный!$K$2&lt;1,"",INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$2))</f>
         <v/>
       </c>
       <c r="E4" s="5" t="s">
@@ -2610,7 +2610,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$2&lt;2,"",INDEX('Досмотр по неделям'!$E$73:$E$98,Служебный!$K$2-1))</f>
+        <f aca="false">IF(Служебный!$K$2&lt;2,"",INDEX('Досмотр по неделям'!$E$80:$E$105,Служебный!$K$2-1))</f>
         <v/>
       </c>
       <c r="C5" s="11" t="str">
@@ -2618,7 +2618,7 @@
         <v>-</v>
       </c>
       <c r="D5" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$2&lt;1,"",INDEX('Досмотр по неделям'!$E$73:$E$98,Служебный!$K$2))</f>
+        <f aca="false">IF(Служебный!$K$2&lt;1,"",INDEX('Досмотр по неделям'!$E$80:$E$105,Служебный!$K$2))</f>
         <v/>
       </c>
       <c r="E5" s="11" t="str">
@@ -2643,7 +2643,7 @@
         <v>11</v>
       </c>
       <c r="B6" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$2&lt;2,"",INDEX('Досмотр по неделям'!$F$73:$F$98,Служебный!$K$2-1))</f>
+        <f aca="false">IF(Служебный!$K$2&lt;2,"",INDEX('Досмотр по неделям'!$F$80:$F$105,Служебный!$K$2-1))</f>
         <v/>
       </c>
       <c r="C6" s="15" t="str">
@@ -2651,7 +2651,7 @@
         <v>-</v>
       </c>
       <c r="D6" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$2&lt;1,"",INDEX('Досмотр по неделям'!$F$73:$F$98,Служебный!$K$2))</f>
+        <f aca="false">IF(Служебный!$K$2&lt;1,"",INDEX('Досмотр по неделям'!$F$80:$F$105,Служебный!$K$2))</f>
         <v/>
       </c>
       <c r="E6" s="15" t="str">
@@ -2676,7 +2676,7 @@
         <v>12</v>
       </c>
       <c r="B7" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$2&lt;2,"",INDEX('Досмотр по неделям'!$G$73:$G$98,Служебный!$K$2-1))</f>
+        <f aca="false">IF(Служебный!$K$2&lt;2,"",INDEX('Досмотр по неделям'!$G$80:$G$105,Служебный!$K$2-1))</f>
         <v/>
       </c>
       <c r="C7" s="15" t="str">
@@ -2684,7 +2684,7 @@
         <v>-</v>
       </c>
       <c r="D7" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$2&lt;1,"",INDEX('Досмотр по неделям'!$G$73:$G$98,Служебный!$K$2))</f>
+        <f aca="false">IF(Служебный!$K$2&lt;1,"",INDEX('Досмотр по неделям'!$G$80:$G$105,Служебный!$K$2))</f>
         <v/>
       </c>
       <c r="E7" s="15" t="str">
@@ -2709,7 +2709,7 @@
         <v>13</v>
       </c>
       <c r="B8" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$2&lt;2,"",INDEX('Досмотр по неделям'!$H$73:$H$98,Служебный!$K$2-1))</f>
+        <f aca="false">IF(Служебный!$K$2&lt;2,"",INDEX('Досмотр по неделям'!$H$80:$H$105,Служебный!$K$2-1))</f>
         <v/>
       </c>
       <c r="C8" s="15" t="str">
@@ -2717,7 +2717,7 @@
         <v>-</v>
       </c>
       <c r="D8" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$2&lt;1,"",INDEX('Досмотр по неделям'!$H$73:$H$98,Служебный!$K$2))</f>
+        <f aca="false">IF(Служебный!$K$2&lt;1,"",INDEX('Досмотр по неделям'!$H$80:$H$105,Служебный!$K$2))</f>
         <v/>
       </c>
       <c r="E8" s="15" t="str">
@@ -2742,7 +2742,7 @@
         <v>14</v>
       </c>
       <c r="B9" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$2&lt;2,"",INDEX('Досмотр по неделям'!$I$73:$I$98,Служебный!$K$2-1))</f>
+        <f aca="false">IF(Служебный!$K$2&lt;2,"",INDEX('Досмотр по неделям'!$I$80:$I$105,Служебный!$K$2-1))</f>
         <v/>
       </c>
       <c r="C9" s="11" t="str">
@@ -2750,7 +2750,7 @@
         <v>-</v>
       </c>
       <c r="D9" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$2&lt;1,"",INDEX('Досмотр по неделям'!$I$73:$I$98,Служебный!$K$2))</f>
+        <f aca="false">IF(Служебный!$K$2&lt;1,"",INDEX('Досмотр по неделям'!$I$80:$I$105,Служебный!$K$2))</f>
         <v/>
       </c>
       <c r="E9" s="11" t="str">
@@ -2775,7 +2775,7 @@
         <v>15</v>
       </c>
       <c r="B10" s="18" t="str">
-        <f aca="false">IF(Служебный!$K$2&lt;2,"",INDEX('Досмотр по неделям'!$J$73:$J$98,Служебный!$K$2-1))</f>
+        <f aca="false">IF(Служебный!$K$2&lt;2,"",INDEX('Досмотр по неделям'!$J$80:$J$105,Служебный!$K$2-1))</f>
         <v/>
       </c>
       <c r="C10" s="19" t="str">
@@ -2783,7 +2783,7 @@
         <v>-</v>
       </c>
       <c r="D10" s="18" t="str">
-        <f aca="false">IF(Служебный!$K$2&lt;1,"",INDEX('Досмотр по неделям'!$J$73:$J$98,Служебный!$K$2))</f>
+        <f aca="false">IF(Служебный!$K$2&lt;1,"",INDEX('Досмотр по неделям'!$J$80:$J$105,Служебный!$K$2))</f>
         <v/>
       </c>
       <c r="E10" s="19" t="str">
@@ -2814,27 +2814,27 @@
         <v>1</v>
       </c>
       <c r="B13" s="2" t="str">
-        <f aca="false">IF(Служебный!$K$7="","Неделя 1","Неделя 1: "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$B$73:$B$98,Служебный!$K$7)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$B$73:$B$98,Служебный!$K$7)),"00")&amp;" - "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$C$73:$C$98,Служебный!$K$7)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$C$73:$C$98,Служебный!$K$7)),"00"))</f>
+        <f aca="false">IF(Служебный!$K$7="","Неделя 1","Неделя 1: "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$B$80:$B$105,Служебный!$K$7)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$B$80:$B$105,Служебный!$K$7)),"00")&amp;" - "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$C$80:$C$105,Служебный!$K$7)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$C$80:$C$105,Служебный!$K$7)),"00"))</f>
         <v>Неделя 1</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="str">
-        <f aca="false">IF(Служебный!$K$8="","Неделя 2","Неделя 2: "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$B$73:$B$98,Служебный!$K$8)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$B$73:$B$98,Служебный!$K$8)),"00")&amp;" - "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$C$73:$C$98,Служебный!$K$8)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$C$73:$C$98,Служебный!$K$8)),"00"))</f>
+        <f aca="false">IF(Служебный!$K$8="","Неделя 2","Неделя 2: "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$B$80:$B$105,Служебный!$K$8)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$B$80:$B$105,Служебный!$K$8)),"00")&amp;" - "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$C$80:$C$105,Служебный!$K$8)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$C$80:$C$105,Служебный!$K$8)),"00"))</f>
         <v>Неделя 2</v>
       </c>
       <c r="E13" s="2"/>
       <c r="F13" s="2" t="str">
-        <f aca="false">IF(Служебный!$K$9="","Неделя 3","Неделя 3: "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$B$73:$B$98,Служебный!$K$9)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$B$73:$B$98,Служебный!$K$9)),"00")&amp;" - "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$C$73:$C$98,Служебный!$K$9)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$C$73:$C$98,Служебный!$K$9)),"00"))</f>
+        <f aca="false">IF(Служебный!$K$9="","Неделя 3","Неделя 3: "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$B$80:$B$105,Служебный!$K$9)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$B$80:$B$105,Служебный!$K$9)),"00")&amp;" - "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$C$80:$C$105,Служебный!$K$9)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$C$80:$C$105,Служебный!$K$9)),"00"))</f>
         <v>Неделя 3</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2" t="str">
-        <f aca="false">IF(Служебный!$K$10="","Неделя 4","Неделя 4: "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$B$73:$B$98,Служебный!$K$10)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$B$73:$B$98,Служебный!$K$10)),"00")&amp;" - "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$C$73:$C$98,Служебный!$K$10)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$C$73:$C$98,Служебный!$K$10)),"00"))</f>
+        <f aca="false">IF(Служебный!$K$10="","Неделя 4","Неделя 4: "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$B$80:$B$105,Служебный!$K$10)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$B$80:$B$105,Служебный!$K$10)),"00")&amp;" - "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$C$80:$C$105,Служебный!$K$10)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$C$80:$C$105,Служебный!$K$10)),"00"))</f>
         <v>Неделя 4</v>
       </c>
       <c r="I13" s="2"/>
       <c r="J13" s="2" t="str">
-        <f aca="false">IF(Служебный!$K$11="","Неделя 5","Неделя 5: "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$B$73:$B$98,Служебный!$K$11)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$B$73:$B$98,Служебный!$K$11)),"00")&amp;" - "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$C$73:$C$98,Служебный!$K$11)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$C$73:$C$98,Служебный!$K$11)),"00"))</f>
+        <f aca="false">IF(Служебный!$K$11="","Неделя 5","Неделя 5: "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$B$80:$B$105,Служебный!$K$11)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$B$80:$B$105,Служебный!$K$11)),"00")&amp;" - "&amp;TEXT(DAY(INDEX('Досмотр по неделям'!$C$80:$C$105,Служебный!$K$11)),"00")&amp;"."&amp;TEXT(MONTH(INDEX('Досмотр по неделям'!$C$80:$C$105,Служебный!$K$11)),"00"))</f>
         <v>Неделя 5</v>
       </c>
       <c r="K13" s="2"/>
@@ -2877,35 +2877,35 @@
         <v>8</v>
       </c>
       <c r="B15" s="4" t="str">
-        <f aca="false">IF(Служебный!$K$7="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$7)="","",INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$7)))</f>
+        <f aca="false">IF(Служебный!$K$7="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$7)="","",INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$7)))</f>
         <v/>
       </c>
       <c r="C15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D15" s="4" t="str">
-        <f aca="false">IF(Служебный!$K$8="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$8)="","",INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$8)))</f>
+        <f aca="false">IF(Служебный!$K$8="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$8)="","",INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$8)))</f>
         <v/>
       </c>
       <c r="E15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="F15" s="4" t="str">
-        <f aca="false">IF(Служебный!$K$9="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$9)="","",INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$9)))</f>
+        <f aca="false">IF(Служебный!$K$9="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$9)="","",INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$9)))</f>
         <v/>
       </c>
       <c r="G15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="H15" s="4" t="str">
-        <f aca="false">IF(Служебный!$K$10="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$10)="","",INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$10)))</f>
+        <f aca="false">IF(Служебный!$K$10="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$10)="","",INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$10)))</f>
         <v/>
       </c>
       <c r="I15" s="5" t="s">
         <v>9</v>
       </c>
       <c r="J15" s="4" t="str">
-        <f aca="false">IF(Служебный!$K$11="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$11)="","",INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$11)))</f>
+        <f aca="false">IF(Служебный!$K$11="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$11)="","",INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$11)))</f>
         <v/>
       </c>
       <c r="K15" s="5" t="s">
@@ -2917,7 +2917,7 @@
         <v>10</v>
       </c>
       <c r="B16" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$7="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$7)="","",INDEX('Досмотр по неделям'!$E$73:$E$98,Служебный!$K$7)))</f>
+        <f aca="false">IF(Служебный!$K$7="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$7)="","",INDEX('Досмотр по неделям'!$E$80:$E$105,Служебный!$K$7)))</f>
         <v/>
       </c>
       <c r="C16" s="23" t="str">
@@ -2925,7 +2925,7 @@
         <v/>
       </c>
       <c r="D16" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$8="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$8)="","",INDEX('Досмотр по неделям'!$E$73:$E$98,Служебный!$K$8)))</f>
+        <f aca="false">IF(Служебный!$K$8="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$8)="","",INDEX('Досмотр по неделям'!$E$80:$E$105,Служебный!$K$8)))</f>
         <v/>
       </c>
       <c r="E16" s="23" t="str">
@@ -2933,7 +2933,7 @@
         <v/>
       </c>
       <c r="F16" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$9="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$9)="","",INDEX('Досмотр по неделям'!$E$73:$E$98,Служебный!$K$9)))</f>
+        <f aca="false">IF(Служебный!$K$9="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$9)="","",INDEX('Досмотр по неделям'!$E$80:$E$105,Служебный!$K$9)))</f>
         <v/>
       </c>
       <c r="G16" s="23" t="str">
@@ -2941,7 +2941,7 @@
         <v/>
       </c>
       <c r="H16" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$10="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$10)="","",INDEX('Досмотр по неделям'!$E$73:$E$98,Служебный!$K$10)))</f>
+        <f aca="false">IF(Служебный!$K$10="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$10)="","",INDEX('Досмотр по неделям'!$E$80:$E$105,Служебный!$K$10)))</f>
         <v/>
       </c>
       <c r="I16" s="23" t="str">
@@ -2949,7 +2949,7 @@
         <v/>
       </c>
       <c r="J16" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$11="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$11)="","",INDEX('Досмотр по неделям'!$E$73:$E$98,Служебный!$K$11)))</f>
+        <f aca="false">IF(Служебный!$K$11="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$11)="","",INDEX('Досмотр по неделям'!$E$80:$E$105,Служебный!$K$11)))</f>
         <v/>
       </c>
       <c r="K16" s="23" t="str">
@@ -2962,7 +2962,7 @@
         <v>11</v>
       </c>
       <c r="B17" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$7="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$7)="","",INDEX('Досмотр по неделям'!$F$73:$F$98,Служебный!$K$7)))</f>
+        <f aca="false">IF(Служебный!$K$7="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$7)="","",INDEX('Досмотр по неделям'!$F$80:$F$105,Служебный!$K$7)))</f>
         <v/>
       </c>
       <c r="C17" s="24" t="str">
@@ -2970,7 +2970,7 @@
         <v/>
       </c>
       <c r="D17" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$8="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$8)="","",INDEX('Досмотр по неделям'!$F$73:$F$98,Служебный!$K$8)))</f>
+        <f aca="false">IF(Служебный!$K$8="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$8)="","",INDEX('Досмотр по неделям'!$F$80:$F$105,Служебный!$K$8)))</f>
         <v/>
       </c>
       <c r="E17" s="24" t="str">
@@ -2978,7 +2978,7 @@
         <v/>
       </c>
       <c r="F17" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$9="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$9)="","",INDEX('Досмотр по неделям'!$F$73:$F$98,Служебный!$K$9)))</f>
+        <f aca="false">IF(Служебный!$K$9="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$9)="","",INDEX('Досмотр по неделям'!$F$80:$F$105,Служебный!$K$9)))</f>
         <v/>
       </c>
       <c r="G17" s="24" t="str">
@@ -2986,7 +2986,7 @@
         <v/>
       </c>
       <c r="H17" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$10="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$10)="","",INDEX('Досмотр по неделям'!$F$73:$F$98,Служебный!$K$10)))</f>
+        <f aca="false">IF(Служебный!$K$10="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$10)="","",INDEX('Досмотр по неделям'!$F$80:$F$105,Служебный!$K$10)))</f>
         <v/>
       </c>
       <c r="I17" s="24" t="str">
@@ -2994,7 +2994,7 @@
         <v/>
       </c>
       <c r="J17" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$11="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$11)="","",INDEX('Досмотр по неделям'!$F$73:$F$98,Служебный!$K$11)))</f>
+        <f aca="false">IF(Служебный!$K$11="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$11)="","",INDEX('Досмотр по неделям'!$F$80:$F$105,Служебный!$K$11)))</f>
         <v/>
       </c>
       <c r="K17" s="24" t="str">
@@ -3007,7 +3007,7 @@
         <v>12</v>
       </c>
       <c r="B18" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$7="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$7)="","",INDEX('Досмотр по неделям'!$G$73:$G$98,Служебный!$K$7)))</f>
+        <f aca="false">IF(Служебный!$K$7="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$7)="","",INDEX('Досмотр по неделям'!$G$80:$G$105,Служебный!$K$7)))</f>
         <v/>
       </c>
       <c r="C18" s="24" t="str">
@@ -3015,7 +3015,7 @@
         <v/>
       </c>
       <c r="D18" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$8="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$8)="","",INDEX('Досмотр по неделям'!$G$73:$G$98,Служебный!$K$8)))</f>
+        <f aca="false">IF(Служебный!$K$8="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$8)="","",INDEX('Досмотр по неделям'!$G$80:$G$105,Служебный!$K$8)))</f>
         <v/>
       </c>
       <c r="E18" s="24" t="str">
@@ -3023,7 +3023,7 @@
         <v/>
       </c>
       <c r="F18" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$9="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$9)="","",INDEX('Досмотр по неделям'!$G$73:$G$98,Служебный!$K$9)))</f>
+        <f aca="false">IF(Служебный!$K$9="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$9)="","",INDEX('Досмотр по неделям'!$G$80:$G$105,Служебный!$K$9)))</f>
         <v/>
       </c>
       <c r="G18" s="24" t="str">
@@ -3031,7 +3031,7 @@
         <v/>
       </c>
       <c r="H18" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$10="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$10)="","",INDEX('Досмотр по неделям'!$G$73:$G$98,Служебный!$K$10)))</f>
+        <f aca="false">IF(Служебный!$K$10="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$10)="","",INDEX('Досмотр по неделям'!$G$80:$G$105,Служебный!$K$10)))</f>
         <v/>
       </c>
       <c r="I18" s="24" t="str">
@@ -3039,7 +3039,7 @@
         <v/>
       </c>
       <c r="J18" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$11="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$11)="","",INDEX('Досмотр по неделям'!$G$73:$G$98,Служебный!$K$11)))</f>
+        <f aca="false">IF(Служебный!$K$11="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$11)="","",INDEX('Досмотр по неделям'!$G$80:$G$105,Служебный!$K$11)))</f>
         <v/>
       </c>
       <c r="K18" s="24" t="str">
@@ -3052,7 +3052,7 @@
         <v>13</v>
       </c>
       <c r="B19" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$7="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$7)="","",INDEX('Досмотр по неделям'!$H$73:$H$98,Служебный!$K$7)))</f>
+        <f aca="false">IF(Служебный!$K$7="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$7)="","",INDEX('Досмотр по неделям'!$H$80:$H$105,Служебный!$K$7)))</f>
         <v/>
       </c>
       <c r="C19" s="24" t="str">
@@ -3060,7 +3060,7 @@
         <v/>
       </c>
       <c r="D19" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$8="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$8)="","",INDEX('Досмотр по неделям'!$H$73:$H$98,Служебный!$K$8)))</f>
+        <f aca="false">IF(Служебный!$K$8="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$8)="","",INDEX('Досмотр по неделям'!$H$80:$H$105,Служебный!$K$8)))</f>
         <v/>
       </c>
       <c r="E19" s="24" t="str">
@@ -3068,7 +3068,7 @@
         <v/>
       </c>
       <c r="F19" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$9="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$9)="","",INDEX('Досмотр по неделям'!$H$73:$H$98,Служебный!$K$9)))</f>
+        <f aca="false">IF(Служебный!$K$9="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$9)="","",INDEX('Досмотр по неделям'!$H$80:$H$105,Служебный!$K$9)))</f>
         <v/>
       </c>
       <c r="G19" s="24" t="str">
@@ -3076,7 +3076,7 @@
         <v/>
       </c>
       <c r="H19" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$10="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$10)="","",INDEX('Досмотр по неделям'!$H$73:$H$98,Служебный!$K$10)))</f>
+        <f aca="false">IF(Служебный!$K$10="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$10)="","",INDEX('Досмотр по неделям'!$H$80:$H$105,Служебный!$K$10)))</f>
         <v/>
       </c>
       <c r="I19" s="24" t="str">
@@ -3084,7 +3084,7 @@
         <v/>
       </c>
       <c r="J19" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$11="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$11)="","",INDEX('Досмотр по неделям'!$H$73:$H$98,Служебный!$K$11)))</f>
+        <f aca="false">IF(Служебный!$K$11="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$11)="","",INDEX('Досмотр по неделям'!$H$80:$H$105,Служебный!$K$11)))</f>
         <v/>
       </c>
       <c r="K19" s="24" t="str">
@@ -3097,7 +3097,7 @@
         <v>14</v>
       </c>
       <c r="B20" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$7="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$7)="","",INDEX('Досмотр по неделям'!$I$73:$I$98,Служебный!$K$7)))</f>
+        <f aca="false">IF(Служебный!$K$7="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$7)="","",INDEX('Досмотр по неделям'!$I$80:$I$105,Служебный!$K$7)))</f>
         <v/>
       </c>
       <c r="C20" s="23" t="str">
@@ -3105,7 +3105,7 @@
         <v/>
       </c>
       <c r="D20" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$8="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$8)="","",INDEX('Досмотр по неделям'!$I$73:$I$98,Служебный!$K$8)))</f>
+        <f aca="false">IF(Служебный!$K$8="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$8)="","",INDEX('Досмотр по неделям'!$I$80:$I$105,Служебный!$K$8)))</f>
         <v/>
       </c>
       <c r="E20" s="23" t="str">
@@ -3113,7 +3113,7 @@
         <v/>
       </c>
       <c r="F20" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$9="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$9)="","",INDEX('Досмотр по неделям'!$I$73:$I$98,Служебный!$K$9)))</f>
+        <f aca="false">IF(Служебный!$K$9="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$9)="","",INDEX('Досмотр по неделям'!$I$80:$I$105,Служебный!$K$9)))</f>
         <v/>
       </c>
       <c r="G20" s="23" t="str">
@@ -3121,7 +3121,7 @@
         <v/>
       </c>
       <c r="H20" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$10="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$10)="","",INDEX('Досмотр по неделям'!$I$73:$I$98,Служебный!$K$10)))</f>
+        <f aca="false">IF(Служебный!$K$10="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$10)="","",INDEX('Досмотр по неделям'!$I$80:$I$105,Служебный!$K$10)))</f>
         <v/>
       </c>
       <c r="I20" s="23" t="str">
@@ -3129,7 +3129,7 @@
         <v/>
       </c>
       <c r="J20" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$11="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$11)="","",INDEX('Досмотр по неделям'!$I$73:$I$98,Служебный!$K$11)))</f>
+        <f aca="false">IF(Служебный!$K$11="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$11)="","",INDEX('Досмотр по неделям'!$I$80:$I$105,Служебный!$K$11)))</f>
         <v/>
       </c>
       <c r="K20" s="23" t="str">
@@ -3142,7 +3142,7 @@
         <v>15</v>
       </c>
       <c r="B21" s="18" t="str">
-        <f aca="false">IF(Служебный!$K$7="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$7)="","",INDEX('Досмотр по неделям'!$J$73:$J$98,Служебный!$K$7)))</f>
+        <f aca="false">IF(Служебный!$K$7="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$7)="","",INDEX('Досмотр по неделям'!$J$80:$J$105,Служебный!$K$7)))</f>
         <v/>
       </c>
       <c r="C21" s="25" t="str">
@@ -3150,7 +3150,7 @@
         <v/>
       </c>
       <c r="D21" s="18" t="str">
-        <f aca="false">IF(Служебный!$K$8="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$8)="","",INDEX('Досмотр по неделям'!$J$73:$J$98,Служебный!$K$8)))</f>
+        <f aca="false">IF(Служебный!$K$8="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$8)="","",INDEX('Досмотр по неделям'!$J$80:$J$105,Служебный!$K$8)))</f>
         <v/>
       </c>
       <c r="E21" s="25" t="str">
@@ -3158,7 +3158,7 @@
         <v/>
       </c>
       <c r="F21" s="18" t="str">
-        <f aca="false">IF(Служебный!$K$9="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$9)="","",INDEX('Досмотр по неделям'!$J$73:$J$98,Служебный!$K$9)))</f>
+        <f aca="false">IF(Служебный!$K$9="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$9)="","",INDEX('Досмотр по неделям'!$J$80:$J$105,Служебный!$K$9)))</f>
         <v/>
       </c>
       <c r="G21" s="25" t="str">
@@ -3166,7 +3166,7 @@
         <v/>
       </c>
       <c r="H21" s="18" t="str">
-        <f aca="false">IF(Служебный!$K$10="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$10)="","",INDEX('Досмотр по неделям'!$J$73:$J$98,Служебный!$K$10)))</f>
+        <f aca="false">IF(Служебный!$K$10="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$10)="","",INDEX('Досмотр по неделям'!$J$80:$J$105,Служебный!$K$10)))</f>
         <v/>
       </c>
       <c r="I21" s="25" t="str">
@@ -3174,7 +3174,7 @@
         <v/>
       </c>
       <c r="J21" s="18" t="str">
-        <f aca="false">IF(Служебный!$K$11="","",IF(INDEX('Досмотр по неделям'!$D$73:$D$98,Служебный!$K$11)="","",INDEX('Досмотр по неделям'!$J$73:$J$98,Служебный!$K$11)))</f>
+        <f aca="false">IF(Служебный!$K$11="","",IF(INDEX('Досмотр по неделям'!$D$80:$D$105,Служебный!$K$11)="","",INDEX('Досмотр по неделям'!$J$80:$J$105,Служебный!$K$11)))</f>
         <v/>
       </c>
       <c r="K21" s="25" t="str">
@@ -3197,12 +3197,12 @@
         <v>1</v>
       </c>
       <c r="B25" s="2" t="str">
-        <f aca="false">IF(Служебный!$K$4="","-",CHOOSE(MONTH(Служебный!$K$4),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(Служебный!$K$4)&amp;" (недель: "&amp;COUNTIFS('Досмотр по неделям'!$B$73:$B$98,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$73:$B$98,"&lt;"&amp;Служебный!$K$3,'Досмотр по неделям'!$D$73:$D$98,"&lt;&gt;")&amp;")")</f>
+        <f aca="false">IF(Служебный!$K$4="","-",CHOOSE(MONTH(Служебный!$K$4),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(Служебный!$K$4)&amp;" (недель: "&amp;COUNTIFS('Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$3,'Досмотр по неделям'!$D$80:$D$105,"&lt;&gt;")&amp;")")</f>
         <v>-</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" s="2" t="str">
-        <f aca="false">IF(Служебный!$K$3="","-",CHOOSE(MONTH(Служебный!$K$3),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(Служебный!$K$3)&amp;" (недель: "&amp;COUNTIFS('Досмотр по неделям'!$B$73:$B$98,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$73:$B$98,"&lt;"&amp;Служебный!$K$5,'Досмотр по неделям'!$D$73:$D$98,"&lt;&gt;")&amp;")")</f>
+        <f aca="false">IF(Служебный!$K$3="","-",CHOOSE(MONTH(Служебный!$K$3),"Январь","Февраль","Март","Апрель","Май","Июнь","Июль","Август","Сентябрь","Октябрь","Ноябрь","Декабрь")&amp;" "&amp;YEAR(Служебный!$K$3)&amp;" (недель: "&amp;COUNTIFS('Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$5,'Досмотр по неделям'!$D$80:$D$105,"&lt;&gt;")&amp;")")</f>
         <v>-</v>
       </c>
       <c r="E25" s="2"/>
@@ -3241,14 +3241,14 @@
         <v>8</v>
       </c>
       <c r="B27" s="4" t="str">
-        <f aca="false">IF(Служебный!$K$4="","",IF(COUNTIFS('Досмотр по неделям'!$B$73:$B$98,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$73:$B$98,"&lt;"&amp;Служебный!$K$3,'Досмотр по неделям'!$D$73:$D$98,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$D$73:$D$98,'Досмотр по неделям'!$B$73:$B$98,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$73:$B$98,"&lt;"&amp;Служебный!$K$3)))</f>
+        <f aca="false">IF(Служебный!$K$4="","",IF(COUNTIFS('Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$3,'Досмотр по неделям'!$D$80:$D$105,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$D$80:$D$105,'Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$3)))</f>
         <v/>
       </c>
       <c r="C27" s="5" t="s">
         <v>9</v>
       </c>
       <c r="D27" s="4" t="str">
-        <f aca="false">IF(Служебный!$K$3="","",IF(COUNTIFS('Досмотр по неделям'!$B$73:$B$98,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$73:$B$98,"&lt;"&amp;Служебный!$K$5,'Досмотр по неделям'!$D$73:$D$98,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$D$73:$D$98,'Досмотр по неделям'!$B$73:$B$98,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$73:$B$98,"&lt;"&amp;Служебный!$K$5)))</f>
+        <f aca="false">IF(Служебный!$K$3="","",IF(COUNTIFS('Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$5,'Досмотр по неделям'!$D$80:$D$105,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$D$80:$D$105,'Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$5)))</f>
         <v/>
       </c>
       <c r="E27" s="5" t="s">
@@ -3271,7 +3271,7 @@
         <v>10</v>
       </c>
       <c r="B28" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$4="","",IF(COUNTIFS('Досмотр по неделям'!$B$73:$B$98,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$73:$B$98,"&lt;"&amp;Служебный!$K$3,'Досмотр по неделям'!$D$73:$D$98,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$E$73:$E$98,'Досмотр по неделям'!$B$73:$B$98,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$73:$B$98,"&lt;"&amp;Служебный!$K$3)))</f>
+        <f aca="false">IF(Служебный!$K$4="","",IF(COUNTIFS('Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$3,'Досмотр по неделям'!$D$80:$D$105,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$E$80:$E$105,'Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$3)))</f>
         <v/>
       </c>
       <c r="C28" s="11" t="str">
@@ -3279,7 +3279,7 @@
         <v>-</v>
       </c>
       <c r="D28" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$3="","",IF(COUNTIFS('Досмотр по неделям'!$B$73:$B$98,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$73:$B$98,"&lt;"&amp;Служебный!$K$5,'Досмотр по неделям'!$D$73:$D$98,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$E$73:$E$98,'Досмотр по неделям'!$B$73:$B$98,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$73:$B$98,"&lt;"&amp;Служебный!$K$5)))</f>
+        <f aca="false">IF(Служебный!$K$3="","",IF(COUNTIFS('Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$5,'Досмотр по неделям'!$D$80:$D$105,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$E$80:$E$105,'Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$5)))</f>
         <v/>
       </c>
       <c r="E28" s="11" t="str">
@@ -3304,7 +3304,7 @@
         <v>11</v>
       </c>
       <c r="B29" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$4="","",IF(COUNTIFS('Досмотр по неделям'!$B$73:$B$98,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$73:$B$98,"&lt;"&amp;Служебный!$K$3,'Досмотр по неделям'!$D$73:$D$98,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$F$73:$F$98,'Досмотр по неделям'!$B$73:$B$98,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$73:$B$98,"&lt;"&amp;Служебный!$K$3)))</f>
+        <f aca="false">IF(Служебный!$K$4="","",IF(COUNTIFS('Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$3,'Досмотр по неделям'!$D$80:$D$105,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$F$80:$F$105,'Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$3)))</f>
         <v/>
       </c>
       <c r="C29" s="15" t="str">
@@ -3312,7 +3312,7 @@
         <v>-</v>
       </c>
       <c r="D29" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$3="","",IF(COUNTIFS('Досмотр по неделям'!$B$73:$B$98,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$73:$B$98,"&lt;"&amp;Служебный!$K$5,'Досмотр по неделям'!$D$73:$D$98,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$F$73:$F$98,'Досмотр по неделям'!$B$73:$B$98,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$73:$B$98,"&lt;"&amp;Служебный!$K$5)))</f>
+        <f aca="false">IF(Служебный!$K$3="","",IF(COUNTIFS('Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$5,'Досмотр по неделям'!$D$80:$D$105,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$F$80:$F$105,'Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$5)))</f>
         <v/>
       </c>
       <c r="E29" s="15" t="str">
@@ -3337,7 +3337,7 @@
         <v>12</v>
       </c>
       <c r="B30" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$4="","",IF(COUNTIFS('Досмотр по неделям'!$B$73:$B$98,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$73:$B$98,"&lt;"&amp;Служебный!$K$3,'Досмотр по неделям'!$D$73:$D$98,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$G$73:$G$98,'Досмотр по неделям'!$B$73:$B$98,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$73:$B$98,"&lt;"&amp;Служебный!$K$3)))</f>
+        <f aca="false">IF(Служебный!$K$4="","",IF(COUNTIFS('Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$3,'Досмотр по неделям'!$D$80:$D$105,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$G$80:$G$105,'Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$3)))</f>
         <v/>
       </c>
       <c r="C30" s="15" t="str">
@@ -3345,7 +3345,7 @@
         <v>-</v>
       </c>
       <c r="D30" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$3="","",IF(COUNTIFS('Досмотр по неделям'!$B$73:$B$98,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$73:$B$98,"&lt;"&amp;Служебный!$K$5,'Досмотр по неделям'!$D$73:$D$98,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$G$73:$G$98,'Досмотр по неделям'!$B$73:$B$98,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$73:$B$98,"&lt;"&amp;Служебный!$K$5)))</f>
+        <f aca="false">IF(Служебный!$K$3="","",IF(COUNTIFS('Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$5,'Досмотр по неделям'!$D$80:$D$105,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$G$80:$G$105,'Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$5)))</f>
         <v/>
       </c>
       <c r="E30" s="15" t="str">
@@ -3370,7 +3370,7 @@
         <v>13</v>
       </c>
       <c r="B31" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$4="","",IF(COUNTIFS('Досмотр по неделям'!$B$73:$B$98,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$73:$B$98,"&lt;"&amp;Служебный!$K$3,'Досмотр по неделям'!$D$73:$D$98,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$H$73:$H$98,'Досмотр по неделям'!$B$73:$B$98,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$73:$B$98,"&lt;"&amp;Служебный!$K$3)))</f>
+        <f aca="false">IF(Служебный!$K$4="","",IF(COUNTIFS('Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$3,'Досмотр по неделям'!$D$80:$D$105,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$H$80:$H$105,'Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$3)))</f>
         <v/>
       </c>
       <c r="C31" s="15" t="str">
@@ -3378,7 +3378,7 @@
         <v>-</v>
       </c>
       <c r="D31" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$3="","",IF(COUNTIFS('Досмотр по неделям'!$B$73:$B$98,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$73:$B$98,"&lt;"&amp;Служебный!$K$5,'Досмотр по неделям'!$D$73:$D$98,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$H$73:$H$98,'Досмотр по неделям'!$B$73:$B$98,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$73:$B$98,"&lt;"&amp;Служебный!$K$5)))</f>
+        <f aca="false">IF(Служебный!$K$3="","",IF(COUNTIFS('Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$5,'Досмотр по неделям'!$D$80:$D$105,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$H$80:$H$105,'Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$5)))</f>
         <v/>
       </c>
       <c r="E31" s="15" t="str">
@@ -3403,7 +3403,7 @@
         <v>14</v>
       </c>
       <c r="B32" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$4="","",IF(COUNTIFS('Досмотр по неделям'!$B$73:$B$98,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$73:$B$98,"&lt;"&amp;Служебный!$K$3,'Досмотр по неделям'!$D$73:$D$98,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$I$73:$I$98,'Досмотр по неделям'!$B$73:$B$98,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$73:$B$98,"&lt;"&amp;Служебный!$K$3)))</f>
+        <f aca="false">IF(Служебный!$K$4="","",IF(COUNTIFS('Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$3,'Досмотр по неделям'!$D$80:$D$105,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$I$80:$I$105,'Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$3)))</f>
         <v/>
       </c>
       <c r="C32" s="11" t="str">
@@ -3411,7 +3411,7 @@
         <v>-</v>
       </c>
       <c r="D32" s="10" t="str">
-        <f aca="false">IF(Служебный!$K$3="","",IF(COUNTIFS('Досмотр по неделям'!$B$73:$B$98,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$73:$B$98,"&lt;"&amp;Служебный!$K$5,'Досмотр по неделям'!$D$73:$D$98,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$I$73:$I$98,'Досмотр по неделям'!$B$73:$B$98,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$73:$B$98,"&lt;"&amp;Служебный!$K$5)))</f>
+        <f aca="false">IF(Служебный!$K$3="","",IF(COUNTIFS('Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$5,'Досмотр по неделям'!$D$80:$D$105,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$I$80:$I$105,'Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$5)))</f>
         <v/>
       </c>
       <c r="E32" s="11" t="str">
@@ -3436,7 +3436,7 @@
         <v>15</v>
       </c>
       <c r="B33" s="18" t="str">
-        <f aca="false">IF(Служебный!$K$4="","",IF(COUNTIFS('Досмотр по неделям'!$B$73:$B$98,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$73:$B$98,"&lt;"&amp;Служебный!$K$3,'Досмотр по неделям'!$D$73:$D$98,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$J$73:$J$98,'Досмотр по неделям'!$B$73:$B$98,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$73:$B$98,"&lt;"&amp;Служебный!$K$3)))</f>
+        <f aca="false">IF(Служебный!$K$4="","",IF(COUNTIFS('Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$3,'Досмотр по неделям'!$D$80:$D$105,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$J$80:$J$105,'Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$4,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$3)))</f>
         <v/>
       </c>
       <c r="C33" s="19" t="str">
@@ -3444,7 +3444,7 @@
         <v>-</v>
       </c>
       <c r="D33" s="18" t="str">
-        <f aca="false">IF(Служебный!$K$3="","",IF(COUNTIFS('Досмотр по неделям'!$B$73:$B$98,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$73:$B$98,"&lt;"&amp;Служебный!$K$5,'Досмотр по неделям'!$D$73:$D$98,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$J$73:$J$98,'Досмотр по неделям'!$B$73:$B$98,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$73:$B$98,"&lt;"&amp;Служебный!$K$5)))</f>
+        <f aca="false">IF(Служебный!$K$3="","",IF(COUNTIFS('Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$5,'Досмотр по неделям'!$D$80:$D$105,"&lt;&gt;")=0,"",SUMIFS('Досмотр по неделям'!$J$80:$J$105,'Досмотр по неделям'!$B$80:$B$105,"&gt;="&amp;Служебный!$K$3,'Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;Служебный!$K$5)))</f>
         <v/>
       </c>
       <c r="E33" s="19" t="str">
@@ -3469,400 +3469,71 @@
         <v>18</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="1" t="s">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A72" s="2" t="s">
+    <row r="79" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B72" s="2" t="s">
+      <c r="B79" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C79" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D72" s="2" t="s">
+      <c r="D79" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="E72" s="2" t="s">
+      <c r="E79" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F72" s="2" t="s">
+      <c r="F79" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G72" s="2" t="s">
+      <c r="G79" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H72" s="2" t="s">
+      <c r="H79" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I72" s="2" t="s">
+      <c r="I79" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J72" s="2" t="s">
+      <c r="J79" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K72" s="2" t="s">
+      <c r="K79" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L72" s="2" t="s">
+      <c r="L79" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M72" s="2" t="s">
+      <c r="M79" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N72" s="2" t="s">
+      <c r="N79" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="O72" s="2" t="s">
+      <c r="O79" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="P72" s="2" t="s">
+      <c r="P79" s="2" t="s">
         <v>29</v>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="27" t="n">
-        <v>1</v>
-      </c>
-      <c r="B73" s="28" t="n">
-        <v>46209</v>
-      </c>
-      <c r="C73" s="29" t="n">
-        <f aca="false">B73+6</f>
-        <v>46215</v>
-      </c>
-      <c r="D73" s="30"/>
-      <c r="E73" s="30"/>
-      <c r="F73" s="30"/>
-      <c r="G73" s="30"/>
-      <c r="H73" s="30"/>
-      <c r="I73" s="30"/>
-      <c r="J73" s="10" t="str">
-        <f aca="false">IF(COUNT(E73:I73)=0,"",SUM(E73:I73))</f>
-        <v/>
-      </c>
-      <c r="K73" s="23" t="str">
-        <f aca="false">IF(OR(D73="",E73="",D73=0),"",E73/D73)</f>
-        <v/>
-      </c>
-      <c r="L73" s="24" t="str">
-        <f aca="false">IF(OR(D73="",F73="",D73=0),"",F73/D73)</f>
-        <v/>
-      </c>
-      <c r="M73" s="24" t="str">
-        <f aca="false">IF(OR(D73="",G73="",D73=0),"",G73/D73)</f>
-        <v/>
-      </c>
-      <c r="N73" s="24" t="str">
-        <f aca="false">IF(OR(D73="",H73="",D73=0),"",H73/D73)</f>
-        <v/>
-      </c>
-      <c r="O73" s="23" t="str">
-        <f aca="false">IF(OR(D73="",I73="",D73=0),"",I73/D73)</f>
-        <v/>
-      </c>
-      <c r="P73" s="24" t="str">
-        <f aca="false">IF(OR(D73="",J73="",D73=0),"",J73/D73)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="27" t="n">
-        <v>2</v>
-      </c>
-      <c r="B74" s="29" t="n">
-        <f aca="false">B73+7</f>
-        <v>46216</v>
-      </c>
-      <c r="C74" s="29" t="n">
-        <f aca="false">B74+6</f>
-        <v>46222</v>
-      </c>
-      <c r="D74" s="30"/>
-      <c r="E74" s="30"/>
-      <c r="F74" s="30"/>
-      <c r="G74" s="30"/>
-      <c r="H74" s="30"/>
-      <c r="I74" s="30"/>
-      <c r="J74" s="10" t="str">
-        <f aca="false">IF(COUNT(E74:I74)=0,"",SUM(E74:I74))</f>
-        <v/>
-      </c>
-      <c r="K74" s="23" t="str">
-        <f aca="false">IF(OR(D74="",E74="",D74=0),"",E74/D74)</f>
-        <v/>
-      </c>
-      <c r="L74" s="24" t="str">
-        <f aca="false">IF(OR(D74="",F74="",D74=0),"",F74/D74)</f>
-        <v/>
-      </c>
-      <c r="M74" s="24" t="str">
-        <f aca="false">IF(OR(D74="",G74="",D74=0),"",G74/D74)</f>
-        <v/>
-      </c>
-      <c r="N74" s="24" t="str">
-        <f aca="false">IF(OR(D74="",H74="",D74=0),"",H74/D74)</f>
-        <v/>
-      </c>
-      <c r="O74" s="23" t="str">
-        <f aca="false">IF(OR(D74="",I74="",D74=0),"",I74/D74)</f>
-        <v/>
-      </c>
-      <c r="P74" s="24" t="str">
-        <f aca="false">IF(OR(D74="",J74="",D74=0),"",J74/D74)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="27" t="n">
-        <v>3</v>
-      </c>
-      <c r="B75" s="29" t="n">
-        <f aca="false">B74+7</f>
-        <v>46223</v>
-      </c>
-      <c r="C75" s="29" t="n">
-        <f aca="false">B75+6</f>
-        <v>46229</v>
-      </c>
-      <c r="D75" s="30"/>
-      <c r="E75" s="30"/>
-      <c r="F75" s="30"/>
-      <c r="G75" s="30"/>
-      <c r="H75" s="30"/>
-      <c r="I75" s="30"/>
-      <c r="J75" s="10" t="str">
-        <f aca="false">IF(COUNT(E75:I75)=0,"",SUM(E75:I75))</f>
-        <v/>
-      </c>
-      <c r="K75" s="23" t="str">
-        <f aca="false">IF(OR(D75="",E75="",D75=0),"",E75/D75)</f>
-        <v/>
-      </c>
-      <c r="L75" s="24" t="str">
-        <f aca="false">IF(OR(D75="",F75="",D75=0),"",F75/D75)</f>
-        <v/>
-      </c>
-      <c r="M75" s="24" t="str">
-        <f aca="false">IF(OR(D75="",G75="",D75=0),"",G75/D75)</f>
-        <v/>
-      </c>
-      <c r="N75" s="24" t="str">
-        <f aca="false">IF(OR(D75="",H75="",D75=0),"",H75/D75)</f>
-        <v/>
-      </c>
-      <c r="O75" s="23" t="str">
-        <f aca="false">IF(OR(D75="",I75="",D75=0),"",I75/D75)</f>
-        <v/>
-      </c>
-      <c r="P75" s="24" t="str">
-        <f aca="false">IF(OR(D75="",J75="",D75=0),"",J75/D75)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="27" t="n">
-        <v>4</v>
-      </c>
-      <c r="B76" s="29" t="n">
-        <f aca="false">B75+7</f>
-        <v>46230</v>
-      </c>
-      <c r="C76" s="29" t="n">
-        <f aca="false">B76+6</f>
-        <v>46236</v>
-      </c>
-      <c r="D76" s="30"/>
-      <c r="E76" s="30"/>
-      <c r="F76" s="30"/>
-      <c r="G76" s="30"/>
-      <c r="H76" s="30"/>
-      <c r="I76" s="30"/>
-      <c r="J76" s="10" t="str">
-        <f aca="false">IF(COUNT(E76:I76)=0,"",SUM(E76:I76))</f>
-        <v/>
-      </c>
-      <c r="K76" s="23" t="str">
-        <f aca="false">IF(OR(D76="",E76="",D76=0),"",E76/D76)</f>
-        <v/>
-      </c>
-      <c r="L76" s="24" t="str">
-        <f aca="false">IF(OR(D76="",F76="",D76=0),"",F76/D76)</f>
-        <v/>
-      </c>
-      <c r="M76" s="24" t="str">
-        <f aca="false">IF(OR(D76="",G76="",D76=0),"",G76/D76)</f>
-        <v/>
-      </c>
-      <c r="N76" s="24" t="str">
-        <f aca="false">IF(OR(D76="",H76="",D76=0),"",H76/D76)</f>
-        <v/>
-      </c>
-      <c r="O76" s="23" t="str">
-        <f aca="false">IF(OR(D76="",I76="",D76=0),"",I76/D76)</f>
-        <v/>
-      </c>
-      <c r="P76" s="24" t="str">
-        <f aca="false">IF(OR(D76="",J76="",D76=0),"",J76/D76)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="27" t="n">
-        <v>5</v>
-      </c>
-      <c r="B77" s="29" t="n">
-        <f aca="false">B76+7</f>
-        <v>46237</v>
-      </c>
-      <c r="C77" s="29" t="n">
-        <f aca="false">B77+6</f>
-        <v>46243</v>
-      </c>
-      <c r="D77" s="30"/>
-      <c r="E77" s="30"/>
-      <c r="F77" s="30"/>
-      <c r="G77" s="30"/>
-      <c r="H77" s="30"/>
-      <c r="I77" s="30"/>
-      <c r="J77" s="10" t="str">
-        <f aca="false">IF(COUNT(E77:I77)=0,"",SUM(E77:I77))</f>
-        <v/>
-      </c>
-      <c r="K77" s="23" t="str">
-        <f aca="false">IF(OR(D77="",E77="",D77=0),"",E77/D77)</f>
-        <v/>
-      </c>
-      <c r="L77" s="24" t="str">
-        <f aca="false">IF(OR(D77="",F77="",D77=0),"",F77/D77)</f>
-        <v/>
-      </c>
-      <c r="M77" s="24" t="str">
-        <f aca="false">IF(OR(D77="",G77="",D77=0),"",G77/D77)</f>
-        <v/>
-      </c>
-      <c r="N77" s="24" t="str">
-        <f aca="false">IF(OR(D77="",H77="",D77=0),"",H77/D77)</f>
-        <v/>
-      </c>
-      <c r="O77" s="23" t="str">
-        <f aca="false">IF(OR(D77="",I77="",D77=0),"",I77/D77)</f>
-        <v/>
-      </c>
-      <c r="P77" s="24" t="str">
-        <f aca="false">IF(OR(D77="",J77="",D77=0),"",J77/D77)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="27" t="n">
-        <v>6</v>
-      </c>
-      <c r="B78" s="29" t="n">
-        <f aca="false">B77+7</f>
-        <v>46244</v>
-      </c>
-      <c r="C78" s="29" t="n">
-        <f aca="false">B78+6</f>
-        <v>46250</v>
-      </c>
-      <c r="D78" s="30"/>
-      <c r="E78" s="30"/>
-      <c r="F78" s="30"/>
-      <c r="G78" s="30"/>
-      <c r="H78" s="30"/>
-      <c r="I78" s="30"/>
-      <c r="J78" s="10" t="str">
-        <f aca="false">IF(COUNT(E78:I78)=0,"",SUM(E78:I78))</f>
-        <v/>
-      </c>
-      <c r="K78" s="23" t="str">
-        <f aca="false">IF(OR(D78="",E78="",D78=0),"",E78/D78)</f>
-        <v/>
-      </c>
-      <c r="L78" s="24" t="str">
-        <f aca="false">IF(OR(D78="",F78="",D78=0),"",F78/D78)</f>
-        <v/>
-      </c>
-      <c r="M78" s="24" t="str">
-        <f aca="false">IF(OR(D78="",G78="",D78=0),"",G78/D78)</f>
-        <v/>
-      </c>
-      <c r="N78" s="24" t="str">
-        <f aca="false">IF(OR(D78="",H78="",D78=0),"",H78/D78)</f>
-        <v/>
-      </c>
-      <c r="O78" s="23" t="str">
-        <f aca="false">IF(OR(D78="",I78="",D78=0),"",I78/D78)</f>
-        <v/>
-      </c>
-      <c r="P78" s="24" t="str">
-        <f aca="false">IF(OR(D78="",J78="",D78=0),"",J78/D78)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="27" t="n">
-        <v>7</v>
-      </c>
-      <c r="B79" s="29" t="n">
-        <f aca="false">B78+7</f>
-        <v>46251</v>
-      </c>
-      <c r="C79" s="29" t="n">
-        <f aca="false">B79+6</f>
-        <v>46257</v>
-      </c>
-      <c r="D79" s="30"/>
-      <c r="E79" s="30"/>
-      <c r="F79" s="30"/>
-      <c r="G79" s="30"/>
-      <c r="H79" s="30"/>
-      <c r="I79" s="30"/>
-      <c r="J79" s="10" t="str">
-        <f aca="false">IF(COUNT(E79:I79)=0,"",SUM(E79:I79))</f>
-        <v/>
-      </c>
-      <c r="K79" s="23" t="str">
-        <f aca="false">IF(OR(D79="",E79="",D79=0),"",E79/D79)</f>
-        <v/>
-      </c>
-      <c r="L79" s="24" t="str">
-        <f aca="false">IF(OR(D79="",F79="",D79=0),"",F79/D79)</f>
-        <v/>
-      </c>
-      <c r="M79" s="24" t="str">
-        <f aca="false">IF(OR(D79="",G79="",D79=0),"",G79/D79)</f>
-        <v/>
-      </c>
-      <c r="N79" s="24" t="str">
-        <f aca="false">IF(OR(D79="",H79="",D79=0),"",H79/D79)</f>
-        <v/>
-      </c>
-      <c r="O79" s="23" t="str">
-        <f aca="false">IF(OR(D79="",I79="",D79=0),"",I79/D79)</f>
-        <v/>
-      </c>
-      <c r="P79" s="24" t="str">
-        <f aca="false">IF(OR(D79="",J79="",D79=0),"",J79/D79)</f>
-        <v/>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="27" t="n">
-        <v>8</v>
-      </c>
-      <c r="B80" s="29" t="n">
-        <f aca="false">B79+7</f>
-        <v>46258</v>
+        <v>1</v>
+      </c>
+      <c r="B80" s="28" t="n">
+        <v>46209</v>
       </c>
       <c r="C80" s="29" t="n">
         <f aca="false">B80+6</f>
-        <v>46264</v>
+        <v>46215</v>
       </c>
       <c r="D80" s="30"/>
       <c r="E80" s="30"/>
@@ -3901,15 +3572,15 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="27" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="B81" s="29" t="n">
         <f aca="false">B80+7</f>
-        <v>46265</v>
+        <v>46216</v>
       </c>
       <c r="C81" s="29" t="n">
         <f aca="false">B81+6</f>
-        <v>46271</v>
+        <v>46222</v>
       </c>
       <c r="D81" s="30"/>
       <c r="E81" s="30"/>
@@ -3948,15 +3619,15 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="27" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B82" s="29" t="n">
         <f aca="false">B81+7</f>
-        <v>46272</v>
+        <v>46223</v>
       </c>
       <c r="C82" s="29" t="n">
         <f aca="false">B82+6</f>
-        <v>46278</v>
+        <v>46229</v>
       </c>
       <c r="D82" s="30"/>
       <c r="E82" s="30"/>
@@ -3995,15 +3666,15 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="27" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B83" s="29" t="n">
         <f aca="false">B82+7</f>
-        <v>46279</v>
+        <v>46230</v>
       </c>
       <c r="C83" s="29" t="n">
         <f aca="false">B83+6</f>
-        <v>46285</v>
+        <v>46236</v>
       </c>
       <c r="D83" s="30"/>
       <c r="E83" s="30"/>
@@ -4042,15 +3713,15 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="27" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B84" s="29" t="n">
         <f aca="false">B83+7</f>
-        <v>46286</v>
+        <v>46237</v>
       </c>
       <c r="C84" s="29" t="n">
         <f aca="false">B84+6</f>
-        <v>46292</v>
+        <v>46243</v>
       </c>
       <c r="D84" s="30"/>
       <c r="E84" s="30"/>
@@ -4089,15 +3760,15 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="27" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B85" s="29" t="n">
         <f aca="false">B84+7</f>
-        <v>46293</v>
+        <v>46244</v>
       </c>
       <c r="C85" s="29" t="n">
         <f aca="false">B85+6</f>
-        <v>46299</v>
+        <v>46250</v>
       </c>
       <c r="D85" s="30"/>
       <c r="E85" s="30"/>
@@ -4136,15 +3807,15 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="27" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B86" s="29" t="n">
         <f aca="false">B85+7</f>
-        <v>46300</v>
+        <v>46251</v>
       </c>
       <c r="C86" s="29" t="n">
         <f aca="false">B86+6</f>
-        <v>46306</v>
+        <v>46257</v>
       </c>
       <c r="D86" s="30"/>
       <c r="E86" s="30"/>
@@ -4183,15 +3854,15 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="27" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="B87" s="29" t="n">
         <f aca="false">B86+7</f>
-        <v>46307</v>
+        <v>46258</v>
       </c>
       <c r="C87" s="29" t="n">
         <f aca="false">B87+6</f>
-        <v>46313</v>
+        <v>46264</v>
       </c>
       <c r="D87" s="30"/>
       <c r="E87" s="30"/>
@@ -4230,15 +3901,15 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="27" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="B88" s="29" t="n">
         <f aca="false">B87+7</f>
-        <v>46314</v>
+        <v>46265</v>
       </c>
       <c r="C88" s="29" t="n">
         <f aca="false">B88+6</f>
-        <v>46320</v>
+        <v>46271</v>
       </c>
       <c r="D88" s="30"/>
       <c r="E88" s="30"/>
@@ -4277,15 +3948,15 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="27" t="n">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="B89" s="29" t="n">
         <f aca="false">B88+7</f>
-        <v>46321</v>
+        <v>46272</v>
       </c>
       <c r="C89" s="29" t="n">
         <f aca="false">B89+6</f>
-        <v>46327</v>
+        <v>46278</v>
       </c>
       <c r="D89" s="30"/>
       <c r="E89" s="30"/>
@@ -4324,15 +3995,15 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="27" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B90" s="29" t="n">
         <f aca="false">B89+7</f>
-        <v>46328</v>
+        <v>46279</v>
       </c>
       <c r="C90" s="29" t="n">
         <f aca="false">B90+6</f>
-        <v>46334</v>
+        <v>46285</v>
       </c>
       <c r="D90" s="30"/>
       <c r="E90" s="30"/>
@@ -4371,15 +4042,15 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="27" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B91" s="29" t="n">
         <f aca="false">B90+7</f>
-        <v>46335</v>
+        <v>46286</v>
       </c>
       <c r="C91" s="29" t="n">
         <f aca="false">B91+6</f>
-        <v>46341</v>
+        <v>46292</v>
       </c>
       <c r="D91" s="30"/>
       <c r="E91" s="30"/>
@@ -4418,15 +4089,15 @@
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="27" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B92" s="29" t="n">
         <f aca="false">B91+7</f>
-        <v>46342</v>
+        <v>46293</v>
       </c>
       <c r="C92" s="29" t="n">
         <f aca="false">B92+6</f>
-        <v>46348</v>
+        <v>46299</v>
       </c>
       <c r="D92" s="30"/>
       <c r="E92" s="30"/>
@@ -4465,15 +4136,15 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="27" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B93" s="29" t="n">
         <f aca="false">B92+7</f>
-        <v>46349</v>
+        <v>46300</v>
       </c>
       <c r="C93" s="29" t="n">
         <f aca="false">B93+6</f>
-        <v>46355</v>
+        <v>46306</v>
       </c>
       <c r="D93" s="30"/>
       <c r="E93" s="30"/>
@@ -4512,15 +4183,15 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="27" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="B94" s="29" t="n">
         <f aca="false">B93+7</f>
-        <v>46356</v>
+        <v>46307</v>
       </c>
       <c r="C94" s="29" t="n">
         <f aca="false">B94+6</f>
-        <v>46362</v>
+        <v>46313</v>
       </c>
       <c r="D94" s="30"/>
       <c r="E94" s="30"/>
@@ -4559,15 +4230,15 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="27" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B95" s="29" t="n">
         <f aca="false">B94+7</f>
-        <v>46363</v>
+        <v>46314</v>
       </c>
       <c r="C95" s="29" t="n">
         <f aca="false">B95+6</f>
-        <v>46369</v>
+        <v>46320</v>
       </c>
       <c r="D95" s="30"/>
       <c r="E95" s="30"/>
@@ -4606,15 +4277,15 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="27" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B96" s="29" t="n">
         <f aca="false">B95+7</f>
-        <v>46370</v>
+        <v>46321</v>
       </c>
       <c r="C96" s="29" t="n">
         <f aca="false">B96+6</f>
-        <v>46376</v>
+        <v>46327</v>
       </c>
       <c r="D96" s="30"/>
       <c r="E96" s="30"/>
@@ -4653,15 +4324,15 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="27" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B97" s="29" t="n">
         <f aca="false">B96+7</f>
-        <v>46377</v>
+        <v>46328</v>
       </c>
       <c r="C97" s="29" t="n">
         <f aca="false">B97+6</f>
-        <v>46383</v>
+        <v>46334</v>
       </c>
       <c r="D97" s="30"/>
       <c r="E97" s="30"/>
@@ -4700,15 +4371,15 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="27" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="B98" s="29" t="n">
         <f aca="false">B97+7</f>
-        <v>46384</v>
+        <v>46335</v>
       </c>
       <c r="C98" s="29" t="n">
         <f aca="false">B98+6</f>
-        <v>46390</v>
+        <v>46341</v>
       </c>
       <c r="D98" s="30"/>
       <c r="E98" s="30"/>
@@ -4745,8 +4416,337 @@
         <v/>
       </c>
     </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="B99" s="29" t="n">
+        <f aca="false">B98+7</f>
+        <v>46342</v>
+      </c>
+      <c r="C99" s="29" t="n">
+        <f aca="false">B99+6</f>
+        <v>46348</v>
+      </c>
+      <c r="D99" s="30"/>
+      <c r="E99" s="30"/>
+      <c r="F99" s="30"/>
+      <c r="G99" s="30"/>
+      <c r="H99" s="30"/>
+      <c r="I99" s="30"/>
+      <c r="J99" s="10" t="str">
+        <f aca="false">IF(COUNT(E99:I99)=0,"",SUM(E99:I99))</f>
+        <v/>
+      </c>
+      <c r="K99" s="23" t="str">
+        <f aca="false">IF(OR(D99="",E99="",D99=0),"",E99/D99)</f>
+        <v/>
+      </c>
+      <c r="L99" s="24" t="str">
+        <f aca="false">IF(OR(D99="",F99="",D99=0),"",F99/D99)</f>
+        <v/>
+      </c>
+      <c r="M99" s="24" t="str">
+        <f aca="false">IF(OR(D99="",G99="",D99=0),"",G99/D99)</f>
+        <v/>
+      </c>
+      <c r="N99" s="24" t="str">
+        <f aca="false">IF(OR(D99="",H99="",D99=0),"",H99/D99)</f>
+        <v/>
+      </c>
+      <c r="O99" s="23" t="str">
+        <f aca="false">IF(OR(D99="",I99="",D99=0),"",I99/D99)</f>
+        <v/>
+      </c>
+      <c r="P99" s="24" t="str">
+        <f aca="false">IF(OR(D99="",J99="",D99=0),"",J99/D99)</f>
+        <v/>
+      </c>
+    </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A100" s="26" t="s">
+      <c r="A100" s="27" t="n">
+        <v>21</v>
+      </c>
+      <c r="B100" s="29" t="n">
+        <f aca="false">B99+7</f>
+        <v>46349</v>
+      </c>
+      <c r="C100" s="29" t="n">
+        <f aca="false">B100+6</f>
+        <v>46355</v>
+      </c>
+      <c r="D100" s="30"/>
+      <c r="E100" s="30"/>
+      <c r="F100" s="30"/>
+      <c r="G100" s="30"/>
+      <c r="H100" s="30"/>
+      <c r="I100" s="30"/>
+      <c r="J100" s="10" t="str">
+        <f aca="false">IF(COUNT(E100:I100)=0,"",SUM(E100:I100))</f>
+        <v/>
+      </c>
+      <c r="K100" s="23" t="str">
+        <f aca="false">IF(OR(D100="",E100="",D100=0),"",E100/D100)</f>
+        <v/>
+      </c>
+      <c r="L100" s="24" t="str">
+        <f aca="false">IF(OR(D100="",F100="",D100=0),"",F100/D100)</f>
+        <v/>
+      </c>
+      <c r="M100" s="24" t="str">
+        <f aca="false">IF(OR(D100="",G100="",D100=0),"",G100/D100)</f>
+        <v/>
+      </c>
+      <c r="N100" s="24" t="str">
+        <f aca="false">IF(OR(D100="",H100="",D100=0),"",H100/D100)</f>
+        <v/>
+      </c>
+      <c r="O100" s="23" t="str">
+        <f aca="false">IF(OR(D100="",I100="",D100=0),"",I100/D100)</f>
+        <v/>
+      </c>
+      <c r="P100" s="24" t="str">
+        <f aca="false">IF(OR(D100="",J100="",D100=0),"",J100/D100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="27" t="n">
+        <v>22</v>
+      </c>
+      <c r="B101" s="29" t="n">
+        <f aca="false">B100+7</f>
+        <v>46356</v>
+      </c>
+      <c r="C101" s="29" t="n">
+        <f aca="false">B101+6</f>
+        <v>46362</v>
+      </c>
+      <c r="D101" s="30"/>
+      <c r="E101" s="30"/>
+      <c r="F101" s="30"/>
+      <c r="G101" s="30"/>
+      <c r="H101" s="30"/>
+      <c r="I101" s="30"/>
+      <c r="J101" s="10" t="str">
+        <f aca="false">IF(COUNT(E101:I101)=0,"",SUM(E101:I101))</f>
+        <v/>
+      </c>
+      <c r="K101" s="23" t="str">
+        <f aca="false">IF(OR(D101="",E101="",D101=0),"",E101/D101)</f>
+        <v/>
+      </c>
+      <c r="L101" s="24" t="str">
+        <f aca="false">IF(OR(D101="",F101="",D101=0),"",F101/D101)</f>
+        <v/>
+      </c>
+      <c r="M101" s="24" t="str">
+        <f aca="false">IF(OR(D101="",G101="",D101=0),"",G101/D101)</f>
+        <v/>
+      </c>
+      <c r="N101" s="24" t="str">
+        <f aca="false">IF(OR(D101="",H101="",D101=0),"",H101/D101)</f>
+        <v/>
+      </c>
+      <c r="O101" s="23" t="str">
+        <f aca="false">IF(OR(D101="",I101="",D101=0),"",I101/D101)</f>
+        <v/>
+      </c>
+      <c r="P101" s="24" t="str">
+        <f aca="false">IF(OR(D101="",J101="",D101=0),"",J101/D101)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="27" t="n">
+        <v>23</v>
+      </c>
+      <c r="B102" s="29" t="n">
+        <f aca="false">B101+7</f>
+        <v>46363</v>
+      </c>
+      <c r="C102" s="29" t="n">
+        <f aca="false">B102+6</f>
+        <v>46369</v>
+      </c>
+      <c r="D102" s="30"/>
+      <c r="E102" s="30"/>
+      <c r="F102" s="30"/>
+      <c r="G102" s="30"/>
+      <c r="H102" s="30"/>
+      <c r="I102" s="30"/>
+      <c r="J102" s="10" t="str">
+        <f aca="false">IF(COUNT(E102:I102)=0,"",SUM(E102:I102))</f>
+        <v/>
+      </c>
+      <c r="K102" s="23" t="str">
+        <f aca="false">IF(OR(D102="",E102="",D102=0),"",E102/D102)</f>
+        <v/>
+      </c>
+      <c r="L102" s="24" t="str">
+        <f aca="false">IF(OR(D102="",F102="",D102=0),"",F102/D102)</f>
+        <v/>
+      </c>
+      <c r="M102" s="24" t="str">
+        <f aca="false">IF(OR(D102="",G102="",D102=0),"",G102/D102)</f>
+        <v/>
+      </c>
+      <c r="N102" s="24" t="str">
+        <f aca="false">IF(OR(D102="",H102="",D102=0),"",H102/D102)</f>
+        <v/>
+      </c>
+      <c r="O102" s="23" t="str">
+        <f aca="false">IF(OR(D102="",I102="",D102=0),"",I102/D102)</f>
+        <v/>
+      </c>
+      <c r="P102" s="24" t="str">
+        <f aca="false">IF(OR(D102="",J102="",D102=0),"",J102/D102)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="27" t="n">
+        <v>24</v>
+      </c>
+      <c r="B103" s="29" t="n">
+        <f aca="false">B102+7</f>
+        <v>46370</v>
+      </c>
+      <c r="C103" s="29" t="n">
+        <f aca="false">B103+6</f>
+        <v>46376</v>
+      </c>
+      <c r="D103" s="30"/>
+      <c r="E103" s="30"/>
+      <c r="F103" s="30"/>
+      <c r="G103" s="30"/>
+      <c r="H103" s="30"/>
+      <c r="I103" s="30"/>
+      <c r="J103" s="10" t="str">
+        <f aca="false">IF(COUNT(E103:I103)=0,"",SUM(E103:I103))</f>
+        <v/>
+      </c>
+      <c r="K103" s="23" t="str">
+        <f aca="false">IF(OR(D103="",E103="",D103=0),"",E103/D103)</f>
+        <v/>
+      </c>
+      <c r="L103" s="24" t="str">
+        <f aca="false">IF(OR(D103="",F103="",D103=0),"",F103/D103)</f>
+        <v/>
+      </c>
+      <c r="M103" s="24" t="str">
+        <f aca="false">IF(OR(D103="",G103="",D103=0),"",G103/D103)</f>
+        <v/>
+      </c>
+      <c r="N103" s="24" t="str">
+        <f aca="false">IF(OR(D103="",H103="",D103=0),"",H103/D103)</f>
+        <v/>
+      </c>
+      <c r="O103" s="23" t="str">
+        <f aca="false">IF(OR(D103="",I103="",D103=0),"",I103/D103)</f>
+        <v/>
+      </c>
+      <c r="P103" s="24" t="str">
+        <f aca="false">IF(OR(D103="",J103="",D103=0),"",J103/D103)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B104" s="29" t="n">
+        <f aca="false">B103+7</f>
+        <v>46377</v>
+      </c>
+      <c r="C104" s="29" t="n">
+        <f aca="false">B104+6</f>
+        <v>46383</v>
+      </c>
+      <c r="D104" s="30"/>
+      <c r="E104" s="30"/>
+      <c r="F104" s="30"/>
+      <c r="G104" s="30"/>
+      <c r="H104" s="30"/>
+      <c r="I104" s="30"/>
+      <c r="J104" s="10" t="str">
+        <f aca="false">IF(COUNT(E104:I104)=0,"",SUM(E104:I104))</f>
+        <v/>
+      </c>
+      <c r="K104" s="23" t="str">
+        <f aca="false">IF(OR(D104="",E104="",D104=0),"",E104/D104)</f>
+        <v/>
+      </c>
+      <c r="L104" s="24" t="str">
+        <f aca="false">IF(OR(D104="",F104="",D104=0),"",F104/D104)</f>
+        <v/>
+      </c>
+      <c r="M104" s="24" t="str">
+        <f aca="false">IF(OR(D104="",G104="",D104=0),"",G104/D104)</f>
+        <v/>
+      </c>
+      <c r="N104" s="24" t="str">
+        <f aca="false">IF(OR(D104="",H104="",D104=0),"",H104/D104)</f>
+        <v/>
+      </c>
+      <c r="O104" s="23" t="str">
+        <f aca="false">IF(OR(D104="",I104="",D104=0),"",I104/D104)</f>
+        <v/>
+      </c>
+      <c r="P104" s="24" t="str">
+        <f aca="false">IF(OR(D104="",J104="",D104=0),"",J104/D104)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B105" s="29" t="n">
+        <f aca="false">B104+7</f>
+        <v>46384</v>
+      </c>
+      <c r="C105" s="29" t="n">
+        <f aca="false">B105+6</f>
+        <v>46390</v>
+      </c>
+      <c r="D105" s="30"/>
+      <c r="E105" s="30"/>
+      <c r="F105" s="30"/>
+      <c r="G105" s="30"/>
+      <c r="H105" s="30"/>
+      <c r="I105" s="30"/>
+      <c r="J105" s="10" t="str">
+        <f aca="false">IF(COUNT(E105:I105)=0,"",SUM(E105:I105))</f>
+        <v/>
+      </c>
+      <c r="K105" s="23" t="str">
+        <f aca="false">IF(OR(D105="",E105="",D105=0),"",E105/D105)</f>
+        <v/>
+      </c>
+      <c r="L105" s="24" t="str">
+        <f aca="false">IF(OR(D105="",F105="",D105=0),"",F105/D105)</f>
+        <v/>
+      </c>
+      <c r="M105" s="24" t="str">
+        <f aca="false">IF(OR(D105="",G105="",D105=0),"",G105/D105)</f>
+        <v/>
+      </c>
+      <c r="N105" s="24" t="str">
+        <f aca="false">IF(OR(D105="",H105="",D105=0),"",H105/D105)</f>
+        <v/>
+      </c>
+      <c r="O105" s="23" t="str">
+        <f aca="false">IF(OR(D105="",I105="",D105=0),"",I105/D105)</f>
+        <v/>
+      </c>
+      <c r="P105" s="24" t="str">
+        <f aca="false">IF(OR(D105="",J105="",D105=0),"",J105/D105)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="26" t="s">
         <v>30</v>
       </c>
     </row>
@@ -4918,82 +4918,82 @@
         <v>34</v>
       </c>
       <c r="K2" s="32" t="n">
-        <f aca="false">COUNT('Досмотр по неделям'!$D$73:$D$98)</f>
+        <f aca="false">COUNT('Досмотр по неделям'!$D$80:$D$105)</f>
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="str">
-        <f aca="false">TEXT(DAY('Досмотр по неделям'!B73),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B73),"00")</f>
+        <f aca="false">TEXT(DAY('Досмотр по неделям'!B80),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B80),"00")</f>
         <v>06.07</v>
       </c>
       <c r="B3" s="10" t="e">
-        <f aca="false">IF('Досмотр по неделям'!D73="",NA(),'Досмотр по неделям'!D73)</f>
+        <f aca="false">IF('Досмотр по неделям'!D80="",NA(),'Досмотр по неделям'!D80)</f>
         <v>#N/A</v>
       </c>
       <c r="C3" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!K73="",'Досмотр по неделям'!K73=0),NA(),'Досмотр по неделям'!K73)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!K80="",'Досмотр по неделям'!K80=0),NA(),'Досмотр по неделям'!K80)</f>
         <v>#N/A</v>
       </c>
       <c r="D3" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!L73="",'Досмотр по неделям'!L73=0),NA(),'Досмотр по неделям'!L73)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!L80="",'Досмотр по неделям'!L80=0),NA(),'Досмотр по неделям'!L80)</f>
         <v>#N/A</v>
       </c>
       <c r="E3" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!M73="",'Досмотр по неделям'!M73=0),NA(),'Досмотр по неделям'!M73)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!M80="",'Досмотр по неделям'!M80=0),NA(),'Досмотр по неделям'!M80)</f>
         <v>#N/A</v>
       </c>
       <c r="F3" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!N73="",'Досмотр по неделям'!N73=0),NA(),'Досмотр по неделям'!N73)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!N80="",'Досмотр по неделям'!N80=0),NA(),'Досмотр по неделям'!N80)</f>
         <v>#N/A</v>
       </c>
       <c r="G3" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!O73="",'Досмотр по неделям'!O73=0),NA(),'Досмотр по неделям'!O73)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!O80="",'Досмотр по неделям'!O80=0),NA(),'Досмотр по неделям'!O80)</f>
         <v>#N/A</v>
       </c>
       <c r="H3" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!P73="",'Досмотр по неделям'!P73=0),NA(),'Досмотр по неделям'!P73)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!P80="",'Досмотр по неделям'!P80=0),NA(),'Досмотр по неделям'!P80)</f>
         <v>#N/A</v>
       </c>
       <c r="J3" s="32" t="s">
         <v>35</v>
       </c>
       <c r="K3" s="33" t="str">
-        <f aca="false">IF(K2=0,"",DATE(YEAR(INDEX('Досмотр по неделям'!$B$73:$B$98,K2)),MONTH(INDEX('Досмотр по неделям'!$B$73:$B$98,K2)),1))</f>
+        <f aca="false">IF(K2=0,"",DATE(YEAR(INDEX('Досмотр по неделям'!$B$80:$B$105,K2)),MONTH(INDEX('Досмотр по неделям'!$B$80:$B$105,K2)),1))</f>
         <v/>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="9" t="str">
-        <f aca="false">TEXT(DAY('Досмотр по неделям'!B74),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B74),"00")</f>
+        <f aca="false">TEXT(DAY('Досмотр по неделям'!B81),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B81),"00")</f>
         <v>13.07</v>
       </c>
       <c r="B4" s="10" t="e">
-        <f aca="false">IF('Досмотр по неделям'!D74="",NA(),'Досмотр по неделям'!D74)</f>
+        <f aca="false">IF('Досмотр по неделям'!D81="",NA(),'Досмотр по неделям'!D81)</f>
         <v>#N/A</v>
       </c>
       <c r="C4" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!K74="",'Досмотр по неделям'!K74=0),NA(),'Досмотр по неделям'!K74)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!K81="",'Досмотр по неделям'!K81=0),NA(),'Досмотр по неделям'!K81)</f>
         <v>#N/A</v>
       </c>
       <c r="D4" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!L74="",'Досмотр по неделям'!L74=0),NA(),'Досмотр по неделям'!L74)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!L81="",'Досмотр по неделям'!L81=0),NA(),'Досмотр по неделям'!L81)</f>
         <v>#N/A</v>
       </c>
       <c r="E4" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!M74="",'Досмотр по неделям'!M74=0),NA(),'Досмотр по неделям'!M74)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!M81="",'Досмотр по неделям'!M81=0),NA(),'Досмотр по неделям'!M81)</f>
         <v>#N/A</v>
       </c>
       <c r="F4" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!N74="",'Досмотр по неделям'!N74=0),NA(),'Досмотр по неделям'!N74)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!N81="",'Досмотр по неделям'!N81=0),NA(),'Досмотр по неделям'!N81)</f>
         <v>#N/A</v>
       </c>
       <c r="G4" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!O74="",'Досмотр по неделям'!O74=0),NA(),'Досмотр по неделям'!O74)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!O81="",'Досмотр по неделям'!O81=0),NA(),'Досмотр по неделям'!O81)</f>
         <v>#N/A</v>
       </c>
       <c r="H4" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!P74="",'Досмотр по неделям'!P74=0),NA(),'Досмотр по неделям'!P74)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!P81="",'Досмотр по неделям'!P81=0),NA(),'Досмотр по неделям'!P81)</f>
         <v>#N/A</v>
       </c>
       <c r="J4" s="32" t="s">
@@ -5006,35 +5006,35 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="str">
-        <f aca="false">TEXT(DAY('Досмотр по неделям'!B75),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B75),"00")</f>
+        <f aca="false">TEXT(DAY('Досмотр по неделям'!B82),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B82),"00")</f>
         <v>20.07</v>
       </c>
       <c r="B5" s="10" t="e">
-        <f aca="false">IF('Досмотр по неделям'!D75="",NA(),'Досмотр по неделям'!D75)</f>
+        <f aca="false">IF('Досмотр по неделям'!D82="",NA(),'Досмотр по неделям'!D82)</f>
         <v>#N/A</v>
       </c>
       <c r="C5" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!K75="",'Досмотр по неделям'!K75=0),NA(),'Досмотр по неделям'!K75)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!K82="",'Досмотр по неделям'!K82=0),NA(),'Досмотр по неделям'!K82)</f>
         <v>#N/A</v>
       </c>
       <c r="D5" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!L75="",'Досмотр по неделям'!L75=0),NA(),'Досмотр по неделям'!L75)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!L82="",'Досмотр по неделям'!L82=0),NA(),'Досмотр по неделям'!L82)</f>
         <v>#N/A</v>
       </c>
       <c r="E5" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!M75="",'Досмотр по неделям'!M75=0),NA(),'Досмотр по неделям'!M75)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!M82="",'Досмотр по неделям'!M82=0),NA(),'Досмотр по неделям'!M82)</f>
         <v>#N/A</v>
       </c>
       <c r="F5" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!N75="",'Досмотр по неделям'!N75=0),NA(),'Досмотр по неделям'!N75)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!N82="",'Досмотр по неделям'!N82=0),NA(),'Досмотр по неделям'!N82)</f>
         <v>#N/A</v>
       </c>
       <c r="G5" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!O75="",'Досмотр по неделям'!O75=0),NA(),'Досмотр по неделям'!O75)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!O82="",'Досмотр по неделям'!O82=0),NA(),'Досмотр по неделям'!O82)</f>
         <v>#N/A</v>
       </c>
       <c r="H5" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!P75="",'Досмотр по неделям'!P75=0),NA(),'Досмотр по неделям'!P75)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!P82="",'Досмотр по неделям'!P82=0),NA(),'Досмотр по неделям'!P82)</f>
         <v>#N/A</v>
       </c>
       <c r="J5" s="32" t="s">
@@ -5047,825 +5047,825 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="str">
-        <f aca="false">TEXT(DAY('Досмотр по неделям'!B76),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B76),"00")</f>
+        <f aca="false">TEXT(DAY('Досмотр по неделям'!B83),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B83),"00")</f>
         <v>27.07</v>
       </c>
       <c r="B6" s="10" t="e">
-        <f aca="false">IF('Досмотр по неделям'!D76="",NA(),'Досмотр по неделям'!D76)</f>
+        <f aca="false">IF('Досмотр по неделям'!D83="",NA(),'Досмотр по неделям'!D83)</f>
         <v>#N/A</v>
       </c>
       <c r="C6" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!K76="",'Досмотр по неделям'!K76=0),NA(),'Досмотр по неделям'!K76)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!K83="",'Досмотр по неделям'!K83=0),NA(),'Досмотр по неделям'!K83)</f>
         <v>#N/A</v>
       </c>
       <c r="D6" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!L76="",'Досмотр по неделям'!L76=0),NA(),'Досмотр по неделям'!L76)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!L83="",'Досмотр по неделям'!L83=0),NA(),'Досмотр по неделям'!L83)</f>
         <v>#N/A</v>
       </c>
       <c r="E6" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!M76="",'Досмотр по неделям'!M76=0),NA(),'Досмотр по неделям'!M76)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!M83="",'Досмотр по неделям'!M83=0),NA(),'Досмотр по неделям'!M83)</f>
         <v>#N/A</v>
       </c>
       <c r="F6" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!N76="",'Досмотр по неделям'!N76=0),NA(),'Досмотр по неделям'!N76)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!N83="",'Досмотр по неделям'!N83=0),NA(),'Досмотр по неделям'!N83)</f>
         <v>#N/A</v>
       </c>
       <c r="G6" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!O76="",'Досмотр по неделям'!O76=0),NA(),'Досмотр по неделям'!O76)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!O83="",'Досмотр по неделям'!O83=0),NA(),'Досмотр по неделям'!O83)</f>
         <v>#N/A</v>
       </c>
       <c r="H6" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!P76="",'Досмотр по неделям'!P76=0),NA(),'Досмотр по неделям'!P76)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!P83="",'Досмотр по неделям'!P83=0),NA(),'Досмотр по неделям'!P83)</f>
         <v>#N/A</v>
       </c>
       <c r="J6" s="32" t="s">
         <v>38</v>
       </c>
       <c r="K6" s="32" t="str">
-        <f aca="false">IF(K3="","",COUNTIF('Досмотр по неделям'!$B$73:$B$98,"&lt;"&amp;K3)+1)</f>
+        <f aca="false">IF(K3="","",COUNTIF('Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;K3)+1)</f>
         <v/>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="str">
-        <f aca="false">TEXT(DAY('Досмотр по неделям'!B77),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B77),"00")</f>
+        <f aca="false">TEXT(DAY('Досмотр по неделям'!B84),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B84),"00")</f>
         <v>03.08</v>
       </c>
       <c r="B7" s="10" t="e">
-        <f aca="false">IF('Досмотр по неделям'!D77="",NA(),'Досмотр по неделям'!D77)</f>
+        <f aca="false">IF('Досмотр по неделям'!D84="",NA(),'Досмотр по неделям'!D84)</f>
         <v>#N/A</v>
       </c>
       <c r="C7" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!K77="",'Досмотр по неделям'!K77=0),NA(),'Досмотр по неделям'!K77)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!K84="",'Досмотр по неделям'!K84=0),NA(),'Досмотр по неделям'!K84)</f>
         <v>#N/A</v>
       </c>
       <c r="D7" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!L77="",'Досмотр по неделям'!L77=0),NA(),'Досмотр по неделям'!L77)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!L84="",'Досмотр по неделям'!L84=0),NA(),'Досмотр по неделям'!L84)</f>
         <v>#N/A</v>
       </c>
       <c r="E7" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!M77="",'Досмотр по неделям'!M77=0),NA(),'Досмотр по неделям'!M77)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!M84="",'Досмотр по неделям'!M84=0),NA(),'Досмотр по неделям'!M84)</f>
         <v>#N/A</v>
       </c>
       <c r="F7" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!N77="",'Досмотр по неделям'!N77=0),NA(),'Досмотр по неделям'!N77)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!N84="",'Досмотр по неделям'!N84=0),NA(),'Досмотр по неделям'!N84)</f>
         <v>#N/A</v>
       </c>
       <c r="G7" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!O77="",'Досмотр по неделям'!O77=0),NA(),'Досмотр по неделям'!O77)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!O84="",'Досмотр по неделям'!O84=0),NA(),'Досмотр по неделям'!O84)</f>
         <v>#N/A</v>
       </c>
       <c r="H7" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!P77="",'Досмотр по неделям'!P77=0),NA(),'Досмотр по неделям'!P77)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!P84="",'Досмотр по неделям'!P84=0),NA(),'Досмотр по неделям'!P84)</f>
         <v>#N/A</v>
       </c>
       <c r="J7" s="32" t="s">
         <v>39</v>
       </c>
       <c r="K7" s="32" t="str">
-        <f aca="false">IF(K6="","",IF(K6+0&gt;26,"",IF(INDEX('Досмотр по неделям'!$B$73:$B$98,K6+0)&lt;K5,K6+0,"")))</f>
+        <f aca="false">IF(K6="","",IF(K6+0&gt;26,"",IF(INDEX('Досмотр по неделям'!$B$80:$B$105,K6+0)&lt;K5,K6+0,"")))</f>
         <v/>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="str">
-        <f aca="false">TEXT(DAY('Досмотр по неделям'!B78),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B78),"00")</f>
+        <f aca="false">TEXT(DAY('Досмотр по неделям'!B85),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B85),"00")</f>
         <v>10.08</v>
       </c>
       <c r="B8" s="10" t="e">
-        <f aca="false">IF('Досмотр по неделям'!D78="",NA(),'Досмотр по неделям'!D78)</f>
+        <f aca="false">IF('Досмотр по неделям'!D85="",NA(),'Досмотр по неделям'!D85)</f>
         <v>#N/A</v>
       </c>
       <c r="C8" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!K78="",'Досмотр по неделям'!K78=0),NA(),'Досмотр по неделям'!K78)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!K85="",'Досмотр по неделям'!K85=0),NA(),'Досмотр по неделям'!K85)</f>
         <v>#N/A</v>
       </c>
       <c r="D8" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!L78="",'Досмотр по неделям'!L78=0),NA(),'Досмотр по неделям'!L78)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!L85="",'Досмотр по неделям'!L85=0),NA(),'Досмотр по неделям'!L85)</f>
         <v>#N/A</v>
       </c>
       <c r="E8" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!M78="",'Досмотр по неделям'!M78=0),NA(),'Досмотр по неделям'!M78)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!M85="",'Досмотр по неделям'!M85=0),NA(),'Досмотр по неделям'!M85)</f>
         <v>#N/A</v>
       </c>
       <c r="F8" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!N78="",'Досмотр по неделям'!N78=0),NA(),'Досмотр по неделям'!N78)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!N85="",'Досмотр по неделям'!N85=0),NA(),'Досмотр по неделям'!N85)</f>
         <v>#N/A</v>
       </c>
       <c r="G8" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!O78="",'Досмотр по неделям'!O78=0),NA(),'Досмотр по неделям'!O78)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!O85="",'Досмотр по неделям'!O85=0),NA(),'Досмотр по неделям'!O85)</f>
         <v>#N/A</v>
       </c>
       <c r="H8" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!P78="",'Досмотр по неделям'!P78=0),NA(),'Досмотр по неделям'!P78)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!P85="",'Досмотр по неделям'!P85=0),NA(),'Досмотр по неделям'!P85)</f>
         <v>#N/A</v>
       </c>
       <c r="J8" s="32" t="s">
         <v>40</v>
       </c>
       <c r="K8" s="32" t="str">
-        <f aca="false">IF(K6="","",IF(K6+1&gt;26,"",IF(INDEX('Досмотр по неделям'!$B$73:$B$98,K6+1)&lt;K5,K6+1,"")))</f>
+        <f aca="false">IF(K6="","",IF(K6+1&gt;26,"",IF(INDEX('Досмотр по неделям'!$B$80:$B$105,K6+1)&lt;K5,K6+1,"")))</f>
         <v/>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="str">
-        <f aca="false">TEXT(DAY('Досмотр по неделям'!B79),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B79),"00")</f>
+        <f aca="false">TEXT(DAY('Досмотр по неделям'!B86),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B86),"00")</f>
         <v>17.08</v>
       </c>
       <c r="B9" s="10" t="e">
-        <f aca="false">IF('Досмотр по неделям'!D79="",NA(),'Досмотр по неделям'!D79)</f>
+        <f aca="false">IF('Досмотр по неделям'!D86="",NA(),'Досмотр по неделям'!D86)</f>
         <v>#N/A</v>
       </c>
       <c r="C9" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!K79="",'Досмотр по неделям'!K79=0),NA(),'Досмотр по неделям'!K79)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!K86="",'Досмотр по неделям'!K86=0),NA(),'Досмотр по неделям'!K86)</f>
         <v>#N/A</v>
       </c>
       <c r="D9" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!L79="",'Досмотр по неделям'!L79=0),NA(),'Досмотр по неделям'!L79)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!L86="",'Досмотр по неделям'!L86=0),NA(),'Досмотр по неделям'!L86)</f>
         <v>#N/A</v>
       </c>
       <c r="E9" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!M79="",'Досмотр по неделям'!M79=0),NA(),'Досмотр по неделям'!M79)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!M86="",'Досмотр по неделям'!M86=0),NA(),'Досмотр по неделям'!M86)</f>
         <v>#N/A</v>
       </c>
       <c r="F9" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!N79="",'Досмотр по неделям'!N79=0),NA(),'Досмотр по неделям'!N79)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!N86="",'Досмотр по неделям'!N86=0),NA(),'Досмотр по неделям'!N86)</f>
         <v>#N/A</v>
       </c>
       <c r="G9" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!O79="",'Досмотр по неделям'!O79=0),NA(),'Досмотр по неделям'!O79)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!O86="",'Досмотр по неделям'!O86=0),NA(),'Досмотр по неделям'!O86)</f>
         <v>#N/A</v>
       </c>
       <c r="H9" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!P79="",'Досмотр по неделям'!P79=0),NA(),'Досмотр по неделям'!P79)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!P86="",'Досмотр по неделям'!P86=0),NA(),'Досмотр по неделям'!P86)</f>
         <v>#N/A</v>
       </c>
       <c r="J9" s="32" t="s">
         <v>41</v>
       </c>
       <c r="K9" s="32" t="str">
-        <f aca="false">IF(K6="","",IF(K6+2&gt;26,"",IF(INDEX('Досмотр по неделям'!$B$73:$B$98,K6+2)&lt;K5,K6+2,"")))</f>
+        <f aca="false">IF(K6="","",IF(K6+2&gt;26,"",IF(INDEX('Досмотр по неделям'!$B$80:$B$105,K6+2)&lt;K5,K6+2,"")))</f>
         <v/>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="str">
-        <f aca="false">TEXT(DAY('Досмотр по неделям'!B80),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B80),"00")</f>
+        <f aca="false">TEXT(DAY('Досмотр по неделям'!B87),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B87),"00")</f>
         <v>24.08</v>
       </c>
       <c r="B10" s="10" t="e">
-        <f aca="false">IF('Досмотр по неделям'!D80="",NA(),'Досмотр по неделям'!D80)</f>
+        <f aca="false">IF('Досмотр по неделям'!D87="",NA(),'Досмотр по неделям'!D87)</f>
         <v>#N/A</v>
       </c>
       <c r="C10" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!K80="",'Досмотр по неделям'!K80=0),NA(),'Досмотр по неделям'!K80)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!K87="",'Досмотр по неделям'!K87=0),NA(),'Досмотр по неделям'!K87)</f>
         <v>#N/A</v>
       </c>
       <c r="D10" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!L80="",'Досмотр по неделям'!L80=0),NA(),'Досмотр по неделям'!L80)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!L87="",'Досмотр по неделям'!L87=0),NA(),'Досмотр по неделям'!L87)</f>
         <v>#N/A</v>
       </c>
       <c r="E10" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!M80="",'Досмотр по неделям'!M80=0),NA(),'Досмотр по неделям'!M80)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!M87="",'Досмотр по неделям'!M87=0),NA(),'Досмотр по неделям'!M87)</f>
         <v>#N/A</v>
       </c>
       <c r="F10" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!N80="",'Досмотр по неделям'!N80=0),NA(),'Досмотр по неделям'!N80)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!N87="",'Досмотр по неделям'!N87=0),NA(),'Досмотр по неделям'!N87)</f>
         <v>#N/A</v>
       </c>
       <c r="G10" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!O80="",'Досмотр по неделям'!O80=0),NA(),'Досмотр по неделям'!O80)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!O87="",'Досмотр по неделям'!O87=0),NA(),'Досмотр по неделям'!O87)</f>
         <v>#N/A</v>
       </c>
       <c r="H10" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!P80="",'Досмотр по неделям'!P80=0),NA(),'Досмотр по неделям'!P80)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!P87="",'Досмотр по неделям'!P87=0),NA(),'Досмотр по неделям'!P87)</f>
         <v>#N/A</v>
       </c>
       <c r="J10" s="32" t="s">
         <v>42</v>
       </c>
       <c r="K10" s="32" t="str">
-        <f aca="false">IF(K6="","",IF(K6+3&gt;26,"",IF(INDEX('Досмотр по неделям'!$B$73:$B$98,K6+3)&lt;K5,K6+3,"")))</f>
+        <f aca="false">IF(K6="","",IF(K6+3&gt;26,"",IF(INDEX('Досмотр по неделям'!$B$80:$B$105,K6+3)&lt;K5,K6+3,"")))</f>
         <v/>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="str">
-        <f aca="false">TEXT(DAY('Досмотр по неделям'!B81),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B81),"00")</f>
+        <f aca="false">TEXT(DAY('Досмотр по неделям'!B88),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B88),"00")</f>
         <v>31.08</v>
       </c>
       <c r="B11" s="10" t="e">
-        <f aca="false">IF('Досмотр по неделям'!D81="",NA(),'Досмотр по неделям'!D81)</f>
+        <f aca="false">IF('Досмотр по неделям'!D88="",NA(),'Досмотр по неделям'!D88)</f>
         <v>#N/A</v>
       </c>
       <c r="C11" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!K81="",'Досмотр по неделям'!K81=0),NA(),'Досмотр по неделям'!K81)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!K88="",'Досмотр по неделям'!K88=0),NA(),'Досмотр по неделям'!K88)</f>
         <v>#N/A</v>
       </c>
       <c r="D11" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!L81="",'Досмотр по неделям'!L81=0),NA(),'Досмотр по неделям'!L81)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!L88="",'Досмотр по неделям'!L88=0),NA(),'Досмотр по неделям'!L88)</f>
         <v>#N/A</v>
       </c>
       <c r="E11" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!M81="",'Досмотр по неделям'!M81=0),NA(),'Досмотр по неделям'!M81)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!M88="",'Досмотр по неделям'!M88=0),NA(),'Досмотр по неделям'!M88)</f>
         <v>#N/A</v>
       </c>
       <c r="F11" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!N81="",'Досмотр по неделям'!N81=0),NA(),'Досмотр по неделям'!N81)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!N88="",'Досмотр по неделям'!N88=0),NA(),'Досмотр по неделям'!N88)</f>
         <v>#N/A</v>
       </c>
       <c r="G11" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!O81="",'Досмотр по неделям'!O81=0),NA(),'Досмотр по неделям'!O81)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!O88="",'Досмотр по неделям'!O88=0),NA(),'Досмотр по неделям'!O88)</f>
         <v>#N/A</v>
       </c>
       <c r="H11" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!P81="",'Досмотр по неделям'!P81=0),NA(),'Досмотр по неделям'!P81)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!P88="",'Досмотр по неделям'!P88=0),NA(),'Досмотр по неделям'!P88)</f>
         <v>#N/A</v>
       </c>
       <c r="J11" s="32" t="s">
         <v>43</v>
       </c>
       <c r="K11" s="32" t="str">
-        <f aca="false">IF(K6="","",IF(K6+4&gt;26,"",IF(INDEX('Досмотр по неделям'!$B$73:$B$98,K6+4)&lt;K5,K6+4,"")))</f>
+        <f aca="false">IF(K6="","",IF(K6+4&gt;26,"",IF(INDEX('Досмотр по неделям'!$B$80:$B$105,K6+4)&lt;K5,K6+4,"")))</f>
         <v/>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="str">
-        <f aca="false">TEXT(DAY('Досмотр по неделям'!B82),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B82),"00")</f>
+        <f aca="false">TEXT(DAY('Досмотр по неделям'!B89),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B89),"00")</f>
         <v>07.09</v>
       </c>
       <c r="B12" s="10" t="e">
-        <f aca="false">IF('Досмотр по неделям'!D82="",NA(),'Досмотр по неделям'!D82)</f>
+        <f aca="false">IF('Досмотр по неделям'!D89="",NA(),'Досмотр по неделям'!D89)</f>
         <v>#N/A</v>
       </c>
       <c r="C12" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!K82="",'Досмотр по неделям'!K82=0),NA(),'Досмотр по неделям'!K82)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!K89="",'Досмотр по неделям'!K89=0),NA(),'Досмотр по неделям'!K89)</f>
         <v>#N/A</v>
       </c>
       <c r="D12" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!L82="",'Досмотр по неделям'!L82=0),NA(),'Досмотр по неделям'!L82)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!L89="",'Досмотр по неделям'!L89=0),NA(),'Досмотр по неделям'!L89)</f>
         <v>#N/A</v>
       </c>
       <c r="E12" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!M82="",'Досмотр по неделям'!M82=0),NA(),'Досмотр по неделям'!M82)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!M89="",'Досмотр по неделям'!M89=0),NA(),'Досмотр по неделям'!M89)</f>
         <v>#N/A</v>
       </c>
       <c r="F12" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!N82="",'Досмотр по неделям'!N82=0),NA(),'Досмотр по неделям'!N82)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!N89="",'Досмотр по неделям'!N89=0),NA(),'Досмотр по неделям'!N89)</f>
         <v>#N/A</v>
       </c>
       <c r="G12" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!O82="",'Досмотр по неделям'!O82=0),NA(),'Досмотр по неделям'!O82)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!O89="",'Досмотр по неделям'!O89=0),NA(),'Досмотр по неделям'!O89)</f>
         <v>#N/A</v>
       </c>
       <c r="H12" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!P82="",'Досмотр по неделям'!P82=0),NA(),'Досмотр по неделям'!P82)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!P89="",'Досмотр по неделям'!P89=0),NA(),'Досмотр по неделям'!P89)</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="str">
-        <f aca="false">TEXT(DAY('Досмотр по неделям'!B83),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B83),"00")</f>
+        <f aca="false">TEXT(DAY('Досмотр по неделям'!B90),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B90),"00")</f>
         <v>14.09</v>
       </c>
       <c r="B13" s="10" t="e">
-        <f aca="false">IF('Досмотр по неделям'!D83="",NA(),'Досмотр по неделям'!D83)</f>
+        <f aca="false">IF('Досмотр по неделям'!D90="",NA(),'Досмотр по неделям'!D90)</f>
         <v>#N/A</v>
       </c>
       <c r="C13" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!K83="",'Досмотр по неделям'!K83=0),NA(),'Досмотр по неделям'!K83)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!K90="",'Досмотр по неделям'!K90=0),NA(),'Досмотр по неделям'!K90)</f>
         <v>#N/A</v>
       </c>
       <c r="D13" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!L83="",'Досмотр по неделям'!L83=0),NA(),'Досмотр по неделям'!L83)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!L90="",'Досмотр по неделям'!L90=0),NA(),'Досмотр по неделям'!L90)</f>
         <v>#N/A</v>
       </c>
       <c r="E13" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!M83="",'Досмотр по неделям'!M83=0),NA(),'Досмотр по неделям'!M83)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!M90="",'Досмотр по неделям'!M90=0),NA(),'Досмотр по неделям'!M90)</f>
         <v>#N/A</v>
       </c>
       <c r="F13" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!N83="",'Досмотр по неделям'!N83=0),NA(),'Досмотр по неделям'!N83)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!N90="",'Досмотр по неделям'!N90=0),NA(),'Досмотр по неделям'!N90)</f>
         <v>#N/A</v>
       </c>
       <c r="G13" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!O83="",'Досмотр по неделям'!O83=0),NA(),'Досмотр по неделям'!O83)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!O90="",'Досмотр по неделям'!O90=0),NA(),'Досмотр по неделям'!O90)</f>
         <v>#N/A</v>
       </c>
       <c r="H13" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!P83="",'Досмотр по неделям'!P83=0),NA(),'Досмотр по неделям'!P83)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!P90="",'Досмотр по неделям'!P90=0),NA(),'Досмотр по неделям'!P90)</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="str">
-        <f aca="false">TEXT(DAY('Досмотр по неделям'!B84),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B84),"00")</f>
+        <f aca="false">TEXT(DAY('Досмотр по неделям'!B91),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B91),"00")</f>
         <v>21.09</v>
       </c>
       <c r="B14" s="10" t="e">
-        <f aca="false">IF('Досмотр по неделям'!D84="",NA(),'Досмотр по неделям'!D84)</f>
+        <f aca="false">IF('Досмотр по неделям'!D91="",NA(),'Досмотр по неделям'!D91)</f>
         <v>#N/A</v>
       </c>
       <c r="C14" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!K84="",'Досмотр по неделям'!K84=0),NA(),'Досмотр по неделям'!K84)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!K91="",'Досмотр по неделям'!K91=0),NA(),'Досмотр по неделям'!K91)</f>
         <v>#N/A</v>
       </c>
       <c r="D14" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!L84="",'Досмотр по неделям'!L84=0),NA(),'Досмотр по неделям'!L84)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!L91="",'Досмотр по неделям'!L91=0),NA(),'Досмотр по неделям'!L91)</f>
         <v>#N/A</v>
       </c>
       <c r="E14" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!M84="",'Досмотр по неделям'!M84=0),NA(),'Досмотр по неделям'!M84)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!M91="",'Досмотр по неделям'!M91=0),NA(),'Досмотр по неделям'!M91)</f>
         <v>#N/A</v>
       </c>
       <c r="F14" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!N84="",'Досмотр по неделям'!N84=0),NA(),'Досмотр по неделям'!N84)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!N91="",'Досмотр по неделям'!N91=0),NA(),'Досмотр по неделям'!N91)</f>
         <v>#N/A</v>
       </c>
       <c r="G14" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!O84="",'Досмотр по неделям'!O84=0),NA(),'Досмотр по неделям'!O84)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!O91="",'Досмотр по неделям'!O91=0),NA(),'Досмотр по неделям'!O91)</f>
         <v>#N/A</v>
       </c>
       <c r="H14" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!P84="",'Досмотр по неделям'!P84=0),NA(),'Досмотр по неделям'!P84)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!P91="",'Досмотр по неделям'!P91=0),NA(),'Досмотр по неделям'!P91)</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="str">
-        <f aca="false">TEXT(DAY('Досмотр по неделям'!B85),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B85),"00")</f>
+        <f aca="false">TEXT(DAY('Досмотр по неделям'!B92),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B92),"00")</f>
         <v>28.09</v>
       </c>
       <c r="B15" s="10" t="e">
-        <f aca="false">IF('Досмотр по неделям'!D85="",NA(),'Досмотр по неделям'!D85)</f>
+        <f aca="false">IF('Досмотр по неделям'!D92="",NA(),'Досмотр по неделям'!D92)</f>
         <v>#N/A</v>
       </c>
       <c r="C15" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!K85="",'Досмотр по неделям'!K85=0),NA(),'Досмотр по неделям'!K85)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!K92="",'Досмотр по неделям'!K92=0),NA(),'Досмотр по неделям'!K92)</f>
         <v>#N/A</v>
       </c>
       <c r="D15" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!L85="",'Досмотр по неделям'!L85=0),NA(),'Досмотр по неделям'!L85)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!L92="",'Досмотр по неделям'!L92=0),NA(),'Досмотр по неделям'!L92)</f>
         <v>#N/A</v>
       </c>
       <c r="E15" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!M85="",'Досмотр по неделям'!M85=0),NA(),'Досмотр по неделям'!M85)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!M92="",'Досмотр по неделям'!M92=0),NA(),'Досмотр по неделям'!M92)</f>
         <v>#N/A</v>
       </c>
       <c r="F15" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!N85="",'Досмотр по неделям'!N85=0),NA(),'Досмотр по неделям'!N85)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!N92="",'Досмотр по неделям'!N92=0),NA(),'Досмотр по неделям'!N92)</f>
         <v>#N/A</v>
       </c>
       <c r="G15" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!O85="",'Досмотр по неделям'!O85=0),NA(),'Досмотр по неделям'!O85)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!O92="",'Досмотр по неделям'!O92=0),NA(),'Досмотр по неделям'!O92)</f>
         <v>#N/A</v>
       </c>
       <c r="H15" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!P85="",'Досмотр по неделям'!P85=0),NA(),'Досмотр по неделям'!P85)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!P92="",'Досмотр по неделям'!P92=0),NA(),'Досмотр по неделям'!P92)</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="str">
-        <f aca="false">TEXT(DAY('Досмотр по неделям'!B86),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B86),"00")</f>
+        <f aca="false">TEXT(DAY('Досмотр по неделям'!B93),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B93),"00")</f>
         <v>05.10</v>
       </c>
       <c r="B16" s="10" t="e">
-        <f aca="false">IF('Досмотр по неделям'!D86="",NA(),'Досмотр по неделям'!D86)</f>
+        <f aca="false">IF('Досмотр по неделям'!D93="",NA(),'Досмотр по неделям'!D93)</f>
         <v>#N/A</v>
       </c>
       <c r="C16" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!K86="",'Досмотр по неделям'!K86=0),NA(),'Досмотр по неделям'!K86)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!K93="",'Досмотр по неделям'!K93=0),NA(),'Досмотр по неделям'!K93)</f>
         <v>#N/A</v>
       </c>
       <c r="D16" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!L86="",'Досмотр по неделям'!L86=0),NA(),'Досмотр по неделям'!L86)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!L93="",'Досмотр по неделям'!L93=0),NA(),'Досмотр по неделям'!L93)</f>
         <v>#N/A</v>
       </c>
       <c r="E16" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!M86="",'Досмотр по неделям'!M86=0),NA(),'Досмотр по неделям'!M86)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!M93="",'Досмотр по неделям'!M93=0),NA(),'Досмотр по неделям'!M93)</f>
         <v>#N/A</v>
       </c>
       <c r="F16" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!N86="",'Досмотр по неделям'!N86=0),NA(),'Досмотр по неделям'!N86)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!N93="",'Досмотр по неделям'!N93=0),NA(),'Досмотр по неделям'!N93)</f>
         <v>#N/A</v>
       </c>
       <c r="G16" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!O86="",'Досмотр по неделям'!O86=0),NA(),'Досмотр по неделям'!O86)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!O93="",'Досмотр по неделям'!O93=0),NA(),'Досмотр по неделям'!O93)</f>
         <v>#N/A</v>
       </c>
       <c r="H16" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!P86="",'Досмотр по неделям'!P86=0),NA(),'Досмотр по неделям'!P86)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!P93="",'Досмотр по неделям'!P93=0),NA(),'Досмотр по неделям'!P93)</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="str">
-        <f aca="false">TEXT(DAY('Досмотр по неделям'!B87),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B87),"00")</f>
+        <f aca="false">TEXT(DAY('Досмотр по неделям'!B94),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B94),"00")</f>
         <v>12.10</v>
       </c>
       <c r="B17" s="10" t="e">
-        <f aca="false">IF('Досмотр по неделям'!D87="",NA(),'Досмотр по неделям'!D87)</f>
+        <f aca="false">IF('Досмотр по неделям'!D94="",NA(),'Досмотр по неделям'!D94)</f>
         <v>#N/A</v>
       </c>
       <c r="C17" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!K87="",'Досмотр по неделям'!K87=0),NA(),'Досмотр по неделям'!K87)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!K94="",'Досмотр по неделям'!K94=0),NA(),'Досмотр по неделям'!K94)</f>
         <v>#N/A</v>
       </c>
       <c r="D17" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!L87="",'Досмотр по неделям'!L87=0),NA(),'Досмотр по неделям'!L87)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!L94="",'Досмотр по неделям'!L94=0),NA(),'Досмотр по неделям'!L94)</f>
         <v>#N/A</v>
       </c>
       <c r="E17" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!M87="",'Досмотр по неделям'!M87=0),NA(),'Досмотр по неделям'!M87)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!M94="",'Досмотр по неделям'!M94=0),NA(),'Досмотр по неделям'!M94)</f>
         <v>#N/A</v>
       </c>
       <c r="F17" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!N87="",'Досмотр по неделям'!N87=0),NA(),'Досмотр по неделям'!N87)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!N94="",'Досмотр по неделям'!N94=0),NA(),'Досмотр по неделям'!N94)</f>
         <v>#N/A</v>
       </c>
       <c r="G17" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!O87="",'Досмотр по неделям'!O87=0),NA(),'Досмотр по неделям'!O87)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!O94="",'Досмотр по неделям'!O94=0),NA(),'Досмотр по неделям'!O94)</f>
         <v>#N/A</v>
       </c>
       <c r="H17" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!P87="",'Досмотр по неделям'!P87=0),NA(),'Досмотр по неделям'!P87)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!P94="",'Досмотр по неделям'!P94=0),NA(),'Досмотр по неделям'!P94)</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="str">
-        <f aca="false">TEXT(DAY('Досмотр по неделям'!B88),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B88),"00")</f>
+        <f aca="false">TEXT(DAY('Досмотр по неделям'!B95),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B95),"00")</f>
         <v>19.10</v>
       </c>
       <c r="B18" s="10" t="e">
-        <f aca="false">IF('Досмотр по неделям'!D88="",NA(),'Досмотр по неделям'!D88)</f>
+        <f aca="false">IF('Досмотр по неделям'!D95="",NA(),'Досмотр по неделям'!D95)</f>
         <v>#N/A</v>
       </c>
       <c r="C18" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!K88="",'Досмотр по неделям'!K88=0),NA(),'Досмотр по неделям'!K88)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!K95="",'Досмотр по неделям'!K95=0),NA(),'Досмотр по неделям'!K95)</f>
         <v>#N/A</v>
       </c>
       <c r="D18" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!L88="",'Досмотр по неделям'!L88=0),NA(),'Досмотр по неделям'!L88)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!L95="",'Досмотр по неделям'!L95=0),NA(),'Досмотр по неделям'!L95)</f>
         <v>#N/A</v>
       </c>
       <c r="E18" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!M88="",'Досмотр по неделям'!M88=0),NA(),'Досмотр по неделям'!M88)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!M95="",'Досмотр по неделям'!M95=0),NA(),'Досмотр по неделям'!M95)</f>
         <v>#N/A</v>
       </c>
       <c r="F18" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!N88="",'Досмотр по неделям'!N88=0),NA(),'Досмотр по неделям'!N88)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!N95="",'Досмотр по неделям'!N95=0),NA(),'Досмотр по неделям'!N95)</f>
         <v>#N/A</v>
       </c>
       <c r="G18" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!O88="",'Досмотр по неделям'!O88=0),NA(),'Досмотр по неделям'!O88)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!O95="",'Досмотр по неделям'!O95=0),NA(),'Досмотр по неделям'!O95)</f>
         <v>#N/A</v>
       </c>
       <c r="H18" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!P88="",'Досмотр по неделям'!P88=0),NA(),'Досмотр по неделям'!P88)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!P95="",'Досмотр по неделям'!P95=0),NA(),'Досмотр по неделям'!P95)</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="str">
-        <f aca="false">TEXT(DAY('Досмотр по неделям'!B89),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B89),"00")</f>
+        <f aca="false">TEXT(DAY('Досмотр по неделям'!B96),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B96),"00")</f>
         <v>26.10</v>
       </c>
       <c r="B19" s="10" t="e">
-        <f aca="false">IF('Досмотр по неделям'!D89="",NA(),'Досмотр по неделям'!D89)</f>
+        <f aca="false">IF('Досмотр по неделям'!D96="",NA(),'Досмотр по неделям'!D96)</f>
         <v>#N/A</v>
       </c>
       <c r="C19" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!K89="",'Досмотр по неделям'!K89=0),NA(),'Досмотр по неделям'!K89)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!K96="",'Досмотр по неделям'!K96=0),NA(),'Досмотр по неделям'!K96)</f>
         <v>#N/A</v>
       </c>
       <c r="D19" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!L89="",'Досмотр по неделям'!L89=0),NA(),'Досмотр по неделям'!L89)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!L96="",'Досмотр по неделям'!L96=0),NA(),'Досмотр по неделям'!L96)</f>
         <v>#N/A</v>
       </c>
       <c r="E19" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!M89="",'Досмотр по неделям'!M89=0),NA(),'Досмотр по неделям'!M89)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!M96="",'Досмотр по неделям'!M96=0),NA(),'Досмотр по неделям'!M96)</f>
         <v>#N/A</v>
       </c>
       <c r="F19" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!N89="",'Досмотр по неделям'!N89=0),NA(),'Досмотр по неделям'!N89)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!N96="",'Досмотр по неделям'!N96=0),NA(),'Досмотр по неделям'!N96)</f>
         <v>#N/A</v>
       </c>
       <c r="G19" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!O89="",'Досмотр по неделям'!O89=0),NA(),'Досмотр по неделям'!O89)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!O96="",'Досмотр по неделям'!O96=0),NA(),'Досмотр по неделям'!O96)</f>
         <v>#N/A</v>
       </c>
       <c r="H19" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!P89="",'Досмотр по неделям'!P89=0),NA(),'Досмотр по неделям'!P89)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!P96="",'Досмотр по неделям'!P96=0),NA(),'Досмотр по неделям'!P96)</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="str">
-        <f aca="false">TEXT(DAY('Досмотр по неделям'!B90),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B90),"00")</f>
+        <f aca="false">TEXT(DAY('Досмотр по неделям'!B97),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B97),"00")</f>
         <v>02.11</v>
       </c>
       <c r="B20" s="10" t="e">
-        <f aca="false">IF('Досмотр по неделям'!D90="",NA(),'Досмотр по неделям'!D90)</f>
+        <f aca="false">IF('Досмотр по неделям'!D97="",NA(),'Досмотр по неделям'!D97)</f>
         <v>#N/A</v>
       </c>
       <c r="C20" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!K90="",'Досмотр по неделям'!K90=0),NA(),'Досмотр по неделям'!K90)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!K97="",'Досмотр по неделям'!K97=0),NA(),'Досмотр по неделям'!K97)</f>
         <v>#N/A</v>
       </c>
       <c r="D20" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!L90="",'Досмотр по неделям'!L90=0),NA(),'Досмотр по неделям'!L90)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!L97="",'Досмотр по неделям'!L97=0),NA(),'Досмотр по неделям'!L97)</f>
         <v>#N/A</v>
       </c>
       <c r="E20" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!M90="",'Досмотр по неделям'!M90=0),NA(),'Досмотр по неделям'!M90)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!M97="",'Досмотр по неделям'!M97=0),NA(),'Досмотр по неделям'!M97)</f>
         <v>#N/A</v>
       </c>
       <c r="F20" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!N90="",'Досмотр по неделям'!N90=0),NA(),'Досмотр по неделям'!N90)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!N97="",'Досмотр по неделям'!N97=0),NA(),'Досмотр по неделям'!N97)</f>
         <v>#N/A</v>
       </c>
       <c r="G20" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!O90="",'Досмотр по неделям'!O90=0),NA(),'Досмотр по неделям'!O90)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!O97="",'Досмотр по неделям'!O97=0),NA(),'Досмотр по неделям'!O97)</f>
         <v>#N/A</v>
       </c>
       <c r="H20" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!P90="",'Досмотр по неделям'!P90=0),NA(),'Досмотр по неделям'!P90)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!P97="",'Досмотр по неделям'!P97=0),NA(),'Досмотр по неделям'!P97)</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="str">
-        <f aca="false">TEXT(DAY('Досмотр по неделям'!B91),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B91),"00")</f>
+        <f aca="false">TEXT(DAY('Досмотр по неделям'!B98),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B98),"00")</f>
         <v>09.11</v>
       </c>
       <c r="B21" s="10" t="e">
-        <f aca="false">IF('Досмотр по неделям'!D91="",NA(),'Досмотр по неделям'!D91)</f>
+        <f aca="false">IF('Досмотр по неделям'!D98="",NA(),'Досмотр по неделям'!D98)</f>
         <v>#N/A</v>
       </c>
       <c r="C21" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!K91="",'Досмотр по неделям'!K91=0),NA(),'Досмотр по неделям'!K91)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!K98="",'Досмотр по неделям'!K98=0),NA(),'Досмотр по неделям'!K98)</f>
         <v>#N/A</v>
       </c>
       <c r="D21" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!L91="",'Досмотр по неделям'!L91=0),NA(),'Досмотр по неделям'!L91)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!L98="",'Досмотр по неделям'!L98=0),NA(),'Досмотр по неделям'!L98)</f>
         <v>#N/A</v>
       </c>
       <c r="E21" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!M91="",'Досмотр по неделям'!M91=0),NA(),'Досмотр по неделям'!M91)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!M98="",'Досмотр по неделям'!M98=0),NA(),'Досмотр по неделям'!M98)</f>
         <v>#N/A</v>
       </c>
       <c r="F21" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!N91="",'Досмотр по неделям'!N91=0),NA(),'Досмотр по неделям'!N91)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!N98="",'Досмотр по неделям'!N98=0),NA(),'Досмотр по неделям'!N98)</f>
         <v>#N/A</v>
       </c>
       <c r="G21" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!O91="",'Досмотр по неделям'!O91=0),NA(),'Досмотр по неделям'!O91)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!O98="",'Досмотр по неделям'!O98=0),NA(),'Досмотр по неделям'!O98)</f>
         <v>#N/A</v>
       </c>
       <c r="H21" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!P91="",'Досмотр по неделям'!P91=0),NA(),'Досмотр по неделям'!P91)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!P98="",'Досмотр по неделям'!P98=0),NA(),'Досмотр по неделям'!P98)</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="str">
-        <f aca="false">TEXT(DAY('Досмотр по неделям'!B92),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B92),"00")</f>
+        <f aca="false">TEXT(DAY('Досмотр по неделям'!B99),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B99),"00")</f>
         <v>16.11</v>
       </c>
       <c r="B22" s="10" t="e">
-        <f aca="false">IF('Досмотр по неделям'!D92="",NA(),'Досмотр по неделям'!D92)</f>
+        <f aca="false">IF('Досмотр по неделям'!D99="",NA(),'Досмотр по неделям'!D99)</f>
         <v>#N/A</v>
       </c>
       <c r="C22" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!K92="",'Досмотр по неделям'!K92=0),NA(),'Досмотр по неделям'!K92)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!K99="",'Досмотр по неделям'!K99=0),NA(),'Досмотр по неделям'!K99)</f>
         <v>#N/A</v>
       </c>
       <c r="D22" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!L92="",'Досмотр по неделям'!L92=0),NA(),'Досмотр по неделям'!L92)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!L99="",'Досмотр по неделям'!L99=0),NA(),'Досмотр по неделям'!L99)</f>
         <v>#N/A</v>
       </c>
       <c r="E22" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!M92="",'Досмотр по неделям'!M92=0),NA(),'Досмотр по неделям'!M92)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!M99="",'Досмотр по неделям'!M99=0),NA(),'Досмотр по неделям'!M99)</f>
         <v>#N/A</v>
       </c>
       <c r="F22" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!N92="",'Досмотр по неделям'!N92=0),NA(),'Досмотр по неделям'!N92)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!N99="",'Досмотр по неделям'!N99=0),NA(),'Досмотр по неделям'!N99)</f>
         <v>#N/A</v>
       </c>
       <c r="G22" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!O92="",'Досмотр по неделям'!O92=0),NA(),'Досмотр по неделям'!O92)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!O99="",'Досмотр по неделям'!O99=0),NA(),'Досмотр по неделям'!O99)</f>
         <v>#N/A</v>
       </c>
       <c r="H22" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!P92="",'Досмотр по неделям'!P92=0),NA(),'Досмотр по неделям'!P92)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!P99="",'Досмотр по неделям'!P99=0),NA(),'Досмотр по неделям'!P99)</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="str">
-        <f aca="false">TEXT(DAY('Досмотр по неделям'!B93),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B93),"00")</f>
+        <f aca="false">TEXT(DAY('Досмотр по неделям'!B100),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B100),"00")</f>
         <v>23.11</v>
       </c>
       <c r="B23" s="10" t="e">
-        <f aca="false">IF('Досмотр по неделям'!D93="",NA(),'Досмотр по неделям'!D93)</f>
+        <f aca="false">IF('Досмотр по неделям'!D100="",NA(),'Досмотр по неделям'!D100)</f>
         <v>#N/A</v>
       </c>
       <c r="C23" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!K93="",'Досмотр по неделям'!K93=0),NA(),'Досмотр по неделям'!K93)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!K100="",'Досмотр по неделям'!K100=0),NA(),'Досмотр по неделям'!K100)</f>
         <v>#N/A</v>
       </c>
       <c r="D23" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!L93="",'Досмотр по неделям'!L93=0),NA(),'Досмотр по неделям'!L93)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!L100="",'Досмотр по неделям'!L100=0),NA(),'Досмотр по неделям'!L100)</f>
         <v>#N/A</v>
       </c>
       <c r="E23" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!M93="",'Досмотр по неделям'!M93=0),NA(),'Досмотр по неделям'!M93)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!M100="",'Досмотр по неделям'!M100=0),NA(),'Досмотр по неделям'!M100)</f>
         <v>#N/A</v>
       </c>
       <c r="F23" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!N93="",'Досмотр по неделям'!N93=0),NA(),'Досмотр по неделям'!N93)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!N100="",'Досмотр по неделям'!N100=0),NA(),'Досмотр по неделям'!N100)</f>
         <v>#N/A</v>
       </c>
       <c r="G23" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!O93="",'Досмотр по неделям'!O93=0),NA(),'Досмотр по неделям'!O93)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!O100="",'Досмотр по неделям'!O100=0),NA(),'Досмотр по неделям'!O100)</f>
         <v>#N/A</v>
       </c>
       <c r="H23" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!P93="",'Досмотр по неделям'!P93=0),NA(),'Досмотр по неделям'!P93)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!P100="",'Досмотр по неделям'!P100=0),NA(),'Досмотр по неделям'!P100)</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="str">
-        <f aca="false">TEXT(DAY('Досмотр по неделям'!B94),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B94),"00")</f>
+        <f aca="false">TEXT(DAY('Досмотр по неделям'!B101),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B101),"00")</f>
         <v>30.11</v>
       </c>
       <c r="B24" s="10" t="e">
-        <f aca="false">IF('Досмотр по неделям'!D94="",NA(),'Досмотр по неделям'!D94)</f>
+        <f aca="false">IF('Досмотр по неделям'!D101="",NA(),'Досмотр по неделям'!D101)</f>
         <v>#N/A</v>
       </c>
       <c r="C24" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!K94="",'Досмотр по неделям'!K94=0),NA(),'Досмотр по неделям'!K94)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!K101="",'Досмотр по неделям'!K101=0),NA(),'Досмотр по неделям'!K101)</f>
         <v>#N/A</v>
       </c>
       <c r="D24" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!L94="",'Досмотр по неделям'!L94=0),NA(),'Досмотр по неделям'!L94)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!L101="",'Досмотр по неделям'!L101=0),NA(),'Досмотр по неделям'!L101)</f>
         <v>#N/A</v>
       </c>
       <c r="E24" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!M94="",'Досмотр по неделям'!M94=0),NA(),'Досмотр по неделям'!M94)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!M101="",'Досмотр по неделям'!M101=0),NA(),'Досмотр по неделям'!M101)</f>
         <v>#N/A</v>
       </c>
       <c r="F24" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!N94="",'Досмотр по неделям'!N94=0),NA(),'Досмотр по неделям'!N94)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!N101="",'Досмотр по неделям'!N101=0),NA(),'Досмотр по неделям'!N101)</f>
         <v>#N/A</v>
       </c>
       <c r="G24" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!O94="",'Досмотр по неделям'!O94=0),NA(),'Досмотр по неделям'!O94)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!O101="",'Досмотр по неделям'!O101=0),NA(),'Досмотр по неделям'!O101)</f>
         <v>#N/A</v>
       </c>
       <c r="H24" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!P94="",'Досмотр по неделям'!P94=0),NA(),'Досмотр по неделям'!P94)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!P101="",'Досмотр по неделям'!P101=0),NA(),'Досмотр по неделям'!P101)</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="str">
-        <f aca="false">TEXT(DAY('Досмотр по неделям'!B95),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B95),"00")</f>
+        <f aca="false">TEXT(DAY('Досмотр по неделям'!B102),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B102),"00")</f>
         <v>07.12</v>
       </c>
       <c r="B25" s="10" t="e">
-        <f aca="false">IF('Досмотр по неделям'!D95="",NA(),'Досмотр по неделям'!D95)</f>
+        <f aca="false">IF('Досмотр по неделям'!D102="",NA(),'Досмотр по неделям'!D102)</f>
         <v>#N/A</v>
       </c>
       <c r="C25" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!K95="",'Досмотр по неделям'!K95=0),NA(),'Досмотр по неделям'!K95)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!K102="",'Досмотр по неделям'!K102=0),NA(),'Досмотр по неделям'!K102)</f>
         <v>#N/A</v>
       </c>
       <c r="D25" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!L95="",'Досмотр по неделям'!L95=0),NA(),'Досмотр по неделям'!L95)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!L102="",'Досмотр по неделям'!L102=0),NA(),'Досмотр по неделям'!L102)</f>
         <v>#N/A</v>
       </c>
       <c r="E25" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!M95="",'Досмотр по неделям'!M95=0),NA(),'Досмотр по неделям'!M95)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!M102="",'Досмотр по неделям'!M102=0),NA(),'Досмотр по неделям'!M102)</f>
         <v>#N/A</v>
       </c>
       <c r="F25" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!N95="",'Досмотр по неделям'!N95=0),NA(),'Досмотр по неделям'!N95)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!N102="",'Досмотр по неделям'!N102=0),NA(),'Досмотр по неделям'!N102)</f>
         <v>#N/A</v>
       </c>
       <c r="G25" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!O95="",'Досмотр по неделям'!O95=0),NA(),'Досмотр по неделям'!O95)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!O102="",'Досмотр по неделям'!O102=0),NA(),'Досмотр по неделям'!O102)</f>
         <v>#N/A</v>
       </c>
       <c r="H25" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!P95="",'Досмотр по неделям'!P95=0),NA(),'Досмотр по неделям'!P95)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!P102="",'Досмотр по неделям'!P102=0),NA(),'Досмотр по неделям'!P102)</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="str">
-        <f aca="false">TEXT(DAY('Досмотр по неделям'!B96),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B96),"00")</f>
+        <f aca="false">TEXT(DAY('Досмотр по неделям'!B103),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B103),"00")</f>
         <v>14.12</v>
       </c>
       <c r="B26" s="10" t="e">
-        <f aca="false">IF('Досмотр по неделям'!D96="",NA(),'Досмотр по неделям'!D96)</f>
+        <f aca="false">IF('Досмотр по неделям'!D103="",NA(),'Досмотр по неделям'!D103)</f>
         <v>#N/A</v>
       </c>
       <c r="C26" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!K96="",'Досмотр по неделям'!K96=0),NA(),'Досмотр по неделям'!K96)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!K103="",'Досмотр по неделям'!K103=0),NA(),'Досмотр по неделям'!K103)</f>
         <v>#N/A</v>
       </c>
       <c r="D26" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!L96="",'Досмотр по неделям'!L96=0),NA(),'Досмотр по неделям'!L96)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!L103="",'Досмотр по неделям'!L103=0),NA(),'Досмотр по неделям'!L103)</f>
         <v>#N/A</v>
       </c>
       <c r="E26" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!M96="",'Досмотр по неделям'!M96=0),NA(),'Досмотр по неделям'!M96)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!M103="",'Досмотр по неделям'!M103=0),NA(),'Досмотр по неделям'!M103)</f>
         <v>#N/A</v>
       </c>
       <c r="F26" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!N96="",'Досмотр по неделям'!N96=0),NA(),'Досмотр по неделям'!N96)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!N103="",'Досмотр по неделям'!N103=0),NA(),'Досмотр по неделям'!N103)</f>
         <v>#N/A</v>
       </c>
       <c r="G26" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!O96="",'Досмотр по неделям'!O96=0),NA(),'Досмотр по неделям'!O96)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!O103="",'Досмотр по неделям'!O103=0),NA(),'Досмотр по неделям'!O103)</f>
         <v>#N/A</v>
       </c>
       <c r="H26" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!P96="",'Досмотр по неделям'!P96=0),NA(),'Досмотр по неделям'!P96)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!P103="",'Досмотр по неделям'!P103=0),NA(),'Досмотр по неделям'!P103)</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="str">
-        <f aca="false">TEXT(DAY('Досмотр по неделям'!B97),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B97),"00")</f>
+        <f aca="false">TEXT(DAY('Досмотр по неделям'!B104),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B104),"00")</f>
         <v>21.12</v>
       </c>
       <c r="B27" s="10" t="e">
-        <f aca="false">IF('Досмотр по неделям'!D97="",NA(),'Досмотр по неделям'!D97)</f>
+        <f aca="false">IF('Досмотр по неделям'!D104="",NA(),'Досмотр по неделям'!D104)</f>
         <v>#N/A</v>
       </c>
       <c r="C27" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!K97="",'Досмотр по неделям'!K97=0),NA(),'Досмотр по неделям'!K97)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!K104="",'Досмотр по неделям'!K104=0),NA(),'Досмотр по неделям'!K104)</f>
         <v>#N/A</v>
       </c>
       <c r="D27" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!L97="",'Досмотр по неделям'!L97=0),NA(),'Досмотр по неделям'!L97)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!L104="",'Досмотр по неделям'!L104=0),NA(),'Досмотр по неделям'!L104)</f>
         <v>#N/A</v>
       </c>
       <c r="E27" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!M97="",'Досмотр по неделям'!M97=0),NA(),'Досмотр по неделям'!M97)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!M104="",'Досмотр по неделям'!M104=0),NA(),'Досмотр по неделям'!M104)</f>
         <v>#N/A</v>
       </c>
       <c r="F27" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!N97="",'Досмотр по неделям'!N97=0),NA(),'Досмотр по неделям'!N97)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!N104="",'Досмотр по неделям'!N104=0),NA(),'Досмотр по неделям'!N104)</f>
         <v>#N/A</v>
       </c>
       <c r="G27" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!O97="",'Досмотр по неделям'!O97=0),NA(),'Досмотр по неделям'!O97)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!O104="",'Досмотр по неделям'!O104=0),NA(),'Досмотр по неделям'!O104)</f>
         <v>#N/A</v>
       </c>
       <c r="H27" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!P97="",'Досмотр по неделям'!P97=0),NA(),'Досмотр по неделям'!P97)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!P104="",'Досмотр по неделям'!P104=0),NA(),'Досмотр по неделям'!P104)</f>
         <v>#N/A</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="str">
-        <f aca="false">TEXT(DAY('Досмотр по неделям'!B98),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B98),"00")</f>
+        <f aca="false">TEXT(DAY('Досмотр по неделям'!B105),"00")&amp;"."&amp;TEXT(MONTH('Досмотр по неделям'!B105),"00")</f>
         <v>28.12</v>
       </c>
       <c r="B28" s="10" t="e">
-        <f aca="false">IF('Досмотр по неделям'!D98="",NA(),'Досмотр по неделям'!D98)</f>
+        <f aca="false">IF('Досмотр по неделям'!D105="",NA(),'Досмотр по неделям'!D105)</f>
         <v>#N/A</v>
       </c>
       <c r="C28" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!K98="",'Досмотр по неделям'!K98=0),NA(),'Досмотр по неделям'!K98)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!K105="",'Досмотр по неделям'!K105=0),NA(),'Досмотр по неделям'!K105)</f>
         <v>#N/A</v>
       </c>
       <c r="D28" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!L98="",'Досмотр по неделям'!L98=0),NA(),'Досмотр по неделям'!L98)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!L105="",'Досмотр по неделям'!L105=0),NA(),'Досмотр по неделям'!L105)</f>
         <v>#N/A</v>
       </c>
       <c r="E28" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!M98="",'Досмотр по неделям'!M98=0),NA(),'Досмотр по неделям'!M98)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!M105="",'Досмотр по неделям'!M105=0),NA(),'Досмотр по неделям'!M105)</f>
         <v>#N/A</v>
       </c>
       <c r="F28" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!N98="",'Досмотр по неделям'!N98=0),NA(),'Досмотр по неделям'!N98)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!N105="",'Досмотр по неделям'!N105=0),NA(),'Досмотр по неделям'!N105)</f>
         <v>#N/A</v>
       </c>
       <c r="G28" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!O98="",'Досмотр по неделям'!O98=0),NA(),'Досмотр по неделям'!O98)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!O105="",'Досмотр по неделям'!O105=0),NA(),'Досмотр по неделям'!O105)</f>
         <v>#N/A</v>
       </c>
       <c r="H28" s="24" t="e">
-        <f aca="false">IF(OR('Досмотр по неделям'!P98="",'Досмотр по неделям'!P98=0),NA(),'Досмотр по неделям'!P98)</f>
+        <f aca="false">IF(OR('Досмотр по неделям'!P105="",'Досмотр по неделям'!P105=0),NA(),'Досмотр по неделям'!P105)</f>
         <v>#N/A</v>
       </c>
     </row>

--- a/Запрещённые_предметы_по_неделям.xlsx
+++ b/Запрещённые_предметы_по_неделям.xlsx
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="103" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="43">
   <si>
     <t xml:space="preserve">Неделя к неделе: последняя заполненная против предыдущей</t>
   </si>
@@ -91,9 +91,6 @@
   </si>
   <si>
     <t xml:space="preserve">Всего попыток проноса</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Цвет конверсии по строке: зелёная неделя с наименьшей долей изъятий, красная с наибольшей.</t>
   </si>
   <si>
     <t xml:space="preserve">Месяц к месяцу: текущий против прошлого</t>
@@ -796,8 +793,8 @@
         </c:ser>
         <c:gapWidth val="40"/>
         <c:overlap val="0"/>
-        <c:axId val="67739032"/>
-        <c:axId val="43901362"/>
+        <c:axId val="72884841"/>
+        <c:axId val="24769284"/>
       </c:barChart>
       <c:lineChart>
         <c:grouping val="standard"/>
@@ -1806,11 +1803,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="1"/>
-        <c:axId val="22705942"/>
-        <c:axId val="43986593"/>
+        <c:axId val="36464924"/>
+        <c:axId val="77184951"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="67739032"/>
+        <c:axId val="72884841"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1843,7 +1840,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43901362"/>
+        <c:crossAx val="24769284"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1851,7 +1848,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="43901362"/>
+        <c:axId val="24769284"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:min val="0"/>
@@ -1918,12 +1915,12 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="67739032"/>
+        <c:crossAx val="72884841"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:catAx>
-        <c:axId val="22705942"/>
+        <c:axId val="36464924"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1956,7 +1953,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="43986593"/>
+        <c:crossAx val="77184951"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1964,7 +1961,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="43986593"/>
+        <c:axId val="77184951"/>
         <c:scaling>
           <c:logBase val="10"/>
           <c:orientation val="minMax"/>
@@ -2033,7 +2030,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="22705942"/>
+        <c:crossAx val="36464924"/>
         <c:crosses val="max"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3182,14 +3179,9 @@
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="26" t="s">
-        <v>16</v>
-      </c>
-    </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -3466,26 +3458,26 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="26" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B79" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B79" s="2" t="s">
+      <c r="C79" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C79" s="2" t="s">
+      <c r="D79" s="2" t="s">
         <v>22</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>23</v>
       </c>
       <c r="E79" s="2" t="s">
         <v>10</v>
@@ -3506,22 +3498,22 @@
         <v>15</v>
       </c>
       <c r="K79" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L79" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="L79" s="2" t="s">
+      <c r="M79" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="M79" s="2" t="s">
+      <c r="N79" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="N79" s="2" t="s">
+      <c r="O79" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="O79" s="2" t="s">
+      <c r="P79" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="P79" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4747,7 +4739,7 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="26" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -4775,83 +4767,11 @@
       <formula>AND(ISNUMBER(F5),F5&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16 E16 G16 I16 K16">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFC6EFCE"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FFFFC7CE"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C17 E17 G17 I17 K17">
-    <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFC6EFCE"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FFFFC7CE"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C18 E18 G18 I18 K18">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFC6EFCE"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FFFFC7CE"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C19 E19 G19 I19 K19">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFC6EFCE"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FFFFC7CE"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C20 E20 G20 I20 K20">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFC6EFCE"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FFFFC7CE"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C21 E21 G21 I21 K21">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="min" val="0"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max" val="0"/>
-        <color rgb="FFC6EFCE"/>
-        <color rgb="FFFFFFFF"/>
-        <color rgb="FFFFC7CE"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="F28:H33">
-    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
       <formula>AND(ISNUMBER(F28),F28&gt;0)</formula>
     </cfRule>
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND(ISNUMBER(F28),F28&lt;0)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4883,18 +4803,18 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="J1" s="31" t="s">
         <v>31</v>
-      </c>
-      <c r="J1" s="31" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>10</v>
@@ -4915,7 +4835,7 @@
         <v>15</v>
       </c>
       <c r="J2" s="32" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="K2" s="32" t="n">
         <f aca="false">COUNT('Досмотр по неделям'!$D$80:$D$105)</f>
@@ -4956,7 +4876,7 @@
         <v>#N/A</v>
       </c>
       <c r="J3" s="32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="K3" s="33" t="str">
         <f aca="false">IF(K2=0,"",DATE(YEAR(INDEX('Досмотр по неделям'!$B$80:$B$105,K2)),MONTH(INDEX('Досмотр по неделям'!$B$80:$B$105,K2)),1))</f>
@@ -4997,7 +4917,7 @@
         <v>#N/A</v>
       </c>
       <c r="J4" s="32" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="K4" s="33" t="str">
         <f aca="false">IF(K3="","",EDATE(K3,-1))</f>
@@ -5038,7 +4958,7 @@
         <v>#N/A</v>
       </c>
       <c r="J5" s="32" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="K5" s="33" t="str">
         <f aca="false">IF(K3="","",EDATE(K3,1))</f>
@@ -5079,7 +4999,7 @@
         <v>#N/A</v>
       </c>
       <c r="J6" s="32" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="K6" s="32" t="str">
         <f aca="false">IF(K3="","",COUNTIF('Досмотр по неделям'!$B$80:$B$105,"&lt;"&amp;K3)+1)</f>
@@ -5120,7 +5040,7 @@
         <v>#N/A</v>
       </c>
       <c r="J7" s="32" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="K7" s="32" t="str">
         <f aca="false">IF(K6="","",IF(K6+0&gt;26,"",IF(INDEX('Досмотр по неделям'!$B$80:$B$105,K6+0)&lt;K5,K6+0,"")))</f>
@@ -5161,7 +5081,7 @@
         <v>#N/A</v>
       </c>
       <c r="J8" s="32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K8" s="32" t="str">
         <f aca="false">IF(K6="","",IF(K6+1&gt;26,"",IF(INDEX('Досмотр по неделям'!$B$80:$B$105,K6+1)&lt;K5,K6+1,"")))</f>
@@ -5202,7 +5122,7 @@
         <v>#N/A</v>
       </c>
       <c r="J9" s="32" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K9" s="32" t="str">
         <f aca="false">IF(K6="","",IF(K6+2&gt;26,"",IF(INDEX('Досмотр по неделям'!$B$80:$B$105,K6+2)&lt;K5,K6+2,"")))</f>
@@ -5243,7 +5163,7 @@
         <v>#N/A</v>
       </c>
       <c r="J10" s="32" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K10" s="32" t="str">
         <f aca="false">IF(K6="","",IF(K6+3&gt;26,"",IF(INDEX('Досмотр по неделям'!$B$80:$B$105,K6+3)&lt;K5,K6+3,"")))</f>
@@ -5284,7 +5204,7 @@
         <v>#N/A</v>
       </c>
       <c r="J11" s="32" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K11" s="32" t="str">
         <f aca="false">IF(K6="","",IF(K6+4&gt;26,"",IF(INDEX('Досмотр по неделям'!$B$80:$B$105,K6+4)&lt;K5,K6+4,"")))</f>
